--- a/BRISAS/EXPENSAS/2026/JUNIO/BRISAS-JUNIO.xlsx
+++ b/BRISAS/EXPENSAS/2026/JUNIO/BRISAS-JUNIO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BRISAS\EXPENSAS\2026\JUNIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{48820830-915A-4D78-8B6A-44D4BF0362F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B13B39-8758-447B-8CCF-C370C6C96B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="479">
   <si>
     <t>Dpto.</t>
   </si>
@@ -1150,9 +1150,6 @@
     <t>TOTAL AL 29/05/2026</t>
   </si>
   <si>
-    <t>Lote 71 deposito el 01/06 $712.000</t>
-  </si>
-  <si>
     <t xml:space="preserve">PERÍODO: JUNIO </t>
   </si>
   <si>
@@ -1473,6 +1470,12 @@
   </si>
   <si>
     <t>SGP - CUIT: 20316550259 - Fc. 000049 - Conexión de agua de alta presion y pase por calle hasta rotonda para riego con llave de paso</t>
+  </si>
+  <si>
+    <t>Lote 71 deposito el 01/06 $712.000 - Luego deposito $710.000 el 30/06</t>
+  </si>
+  <si>
+    <t>Deposito $885.000 30/06</t>
   </si>
 </sst>
 </file>
@@ -2851,14 +2854,94 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2893,99 +2976,33 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3044,24 +3061,10 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3488,34 +3491,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="378"/>
-      <c r="B1" s="373" t="s">
+      <c r="A1" s="406"/>
+      <c r="B1" s="401" t="s">
         <v>155</v>
       </c>
-      <c r="C1" s="374"/>
-      <c r="D1" s="374"/>
-      <c r="E1" s="375"/>
+      <c r="C1" s="402"/>
+      <c r="D1" s="402"/>
+      <c r="E1" s="403"/>
     </row>
     <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="379"/>
-      <c r="B2" s="373" t="s">
+      <c r="A2" s="407"/>
+      <c r="B2" s="401" t="s">
         <v>157</v>
       </c>
-      <c r="C2" s="374"/>
-      <c r="D2" s="374"/>
-      <c r="E2" s="375"/>
+      <c r="C2" s="402"/>
+      <c r="D2" s="402"/>
+      <c r="E2" s="403"/>
     </row>
     <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="379"/>
-      <c r="B3" s="370" t="s">
+      <c r="A3" s="407"/>
+      <c r="B3" s="398" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="371"/>
-      <c r="D3" s="371"/>
-      <c r="E3" s="372"/>
+      <c r="C3" s="399"/>
+      <c r="D3" s="399"/>
+      <c r="E3" s="400"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="379"/>
+      <c r="A4" s="407"/>
       <c r="B4" s="45" t="s">
         <v>154</v>
       </c>
@@ -3524,16 +3527,16 @@
       <c r="E4" s="44"/>
     </row>
     <row r="5" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="379"/>
+      <c r="A5" s="407"/>
       <c r="B5" s="48" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C5" s="46"/>
       <c r="D5" s="46"/>
       <c r="E5" s="47"/>
     </row>
     <row r="6" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="379"/>
+      <c r="A6" s="407"/>
       <c r="B6" s="49" t="s">
         <v>282</v>
       </c>
@@ -3542,7 +3545,7 @@
       <c r="E6" s="47"/>
     </row>
     <row r="7" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="379"/>
+      <c r="A7" s="407"/>
       <c r="B7" s="49" t="s">
         <v>281</v>
       </c>
@@ -3551,13 +3554,13 @@
       <c r="E7" s="47"/>
     </row>
     <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="380"/>
-      <c r="B8" s="376" t="s">
+      <c r="A8" s="408"/>
+      <c r="B8" s="404" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="376"/>
-      <c r="D8" s="376"/>
-      <c r="E8" s="377"/>
+      <c r="C8" s="404"/>
+      <c r="D8" s="404"/>
+      <c r="E8" s="405"/>
     </row>
     <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="32"/>
@@ -3567,27 +3570,27 @@
       <c r="E9" s="32"/>
     </row>
     <row r="10" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="381" t="s">
-        <v>408</v>
-      </c>
-      <c r="B10" s="382"/>
-      <c r="C10" s="382"/>
-      <c r="D10" s="382"/>
-      <c r="E10" s="383"/>
+      <c r="A10" s="383" t="s">
+        <v>407</v>
+      </c>
+      <c r="B10" s="384"/>
+      <c r="C10" s="384"/>
+      <c r="D10" s="384"/>
+      <c r="E10" s="385"/>
     </row>
     <row r="11" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="384"/>
-      <c r="B11" s="385"/>
-      <c r="C11" s="385"/>
-      <c r="D11" s="385"/>
-      <c r="E11" s="386"/>
+      <c r="A11" s="386"/>
+      <c r="B11" s="387"/>
+      <c r="C11" s="387"/>
+      <c r="D11" s="387"/>
+      <c r="E11" s="388"/>
     </row>
     <row r="12" spans="1:5" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="387"/>
-      <c r="B12" s="388"/>
-      <c r="C12" s="388"/>
-      <c r="D12" s="388"/>
-      <c r="E12" s="389"/>
+      <c r="A12" s="389"/>
+      <c r="B12" s="390"/>
+      <c r="C12" s="390"/>
+      <c r="D12" s="390"/>
+      <c r="E12" s="391"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="32"/>
@@ -3604,34 +3607,34 @@
       <c r="E14" s="32"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="390" t="s">
+      <c r="A15" s="392" t="s">
         <v>240</v>
       </c>
-      <c r="B15" s="390"/>
-      <c r="C15" s="390"/>
-      <c r="D15" s="390"/>
-      <c r="E15" s="390"/>
+      <c r="B15" s="392"/>
+      <c r="C15" s="392"/>
+      <c r="D15" s="392"/>
+      <c r="E15" s="392"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="390"/>
-      <c r="B16" s="390"/>
-      <c r="C16" s="390"/>
-      <c r="D16" s="390"/>
-      <c r="E16" s="390"/>
+      <c r="A16" s="392"/>
+      <c r="B16" s="392"/>
+      <c r="C16" s="392"/>
+      <c r="D16" s="392"/>
+      <c r="E16" s="392"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="390"/>
-      <c r="B17" s="390"/>
-      <c r="C17" s="390"/>
-      <c r="D17" s="390"/>
-      <c r="E17" s="390"/>
+      <c r="A17" s="392"/>
+      <c r="B17" s="392"/>
+      <c r="C17" s="392"/>
+      <c r="D17" s="392"/>
+      <c r="E17" s="392"/>
     </row>
     <row r="18" spans="1:8" ht="243" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="390"/>
-      <c r="B18" s="390"/>
-      <c r="C18" s="390"/>
-      <c r="D18" s="390"/>
-      <c r="E18" s="390"/>
+      <c r="A18" s="392"/>
+      <c r="B18" s="392"/>
+      <c r="C18" s="392"/>
+      <c r="D18" s="392"/>
+      <c r="E18" s="392"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="32"/>
@@ -3678,7 +3681,7 @@
     </row>
     <row r="24" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="192" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B24" s="270"/>
       <c r="C24" s="24"/>
@@ -3692,10 +3695,10 @@
       <c r="G24" s="272"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="391" t="s">
-        <v>373</v>
-      </c>
-      <c r="B25" s="392"/>
+      <c r="A25" s="394" t="s">
+        <v>372</v>
+      </c>
+      <c r="B25" s="395"/>
       <c r="C25" s="24"/>
       <c r="D25" s="271">
         <v>-739800.57</v>
@@ -3705,10 +3708,10 @@
       <c r="G25" s="273"/>
     </row>
     <row r="26" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="393" t="s">
-        <v>374</v>
-      </c>
-      <c r="B26" s="394"/>
+      <c r="A26" s="396" t="s">
+        <v>373</v>
+      </c>
+      <c r="B26" s="397"/>
       <c r="C26" s="24"/>
       <c r="D26" s="271">
         <v>0.69</v>
@@ -3734,7 +3737,7 @@
     </row>
     <row r="28" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="365" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B28" s="366"/>
       <c r="C28" s="24"/>
@@ -3742,7 +3745,7 @@
         <v>1520000</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F28" s="32"/>
       <c r="G28" s="273">
@@ -3791,7 +3794,7 @@
     </row>
     <row r="32" spans="1:8" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="24" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B32" s="24"/>
       <c r="C32" s="100"/>
@@ -3806,7 +3809,7 @@
     </row>
     <row r="33" spans="1:9" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="101" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B33" s="24" t="s">
         <v>11</v>
@@ -3970,15 +3973,15 @@
     </row>
     <row r="44" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="365" t="s">
-        <v>432</v>
-      </c>
-      <c r="B44" s="369"/>
+        <v>431</v>
+      </c>
+      <c r="B44" s="393"/>
       <c r="C44" s="104"/>
       <c r="D44" s="256">
         <v>47492852.960000001</v>
       </c>
       <c r="E44" s="28" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F44" s="276">
         <f>D44+D138+D140+D139</f>
@@ -3989,9 +3992,9 @@
     </row>
     <row r="45" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="365" t="s">
-        <v>422</v>
-      </c>
-      <c r="B45" s="369"/>
+        <v>421</v>
+      </c>
+      <c r="B45" s="393"/>
       <c r="C45" s="104"/>
       <c r="D45" s="256">
         <v>5892398.1600000001</v>
@@ -4033,37 +4036,37 @@
       <c r="A48" s="365" t="s">
         <v>332</v>
       </c>
-      <c r="B48" s="369"/>
+      <c r="B48" s="393"/>
       <c r="C48" s="104"/>
       <c r="D48" s="256">
         <v>1472058.6</v>
       </c>
       <c r="E48" s="31" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F48" s="32"/>
       <c r="G48" s="32"/>
     </row>
     <row r="49" spans="1:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="365" t="s">
-        <v>415</v>
-      </c>
-      <c r="B49" s="369"/>
+        <v>414</v>
+      </c>
+      <c r="B49" s="393"/>
       <c r="C49" s="104"/>
       <c r="D49" s="256">
         <v>909920</v>
       </c>
       <c r="E49" s="31" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F49" s="32"/>
       <c r="G49" s="32"/>
     </row>
     <row r="50" spans="1:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="365" t="s">
-        <v>453</v>
-      </c>
-      <c r="B50" s="369"/>
+        <v>452</v>
+      </c>
+      <c r="B50" s="393"/>
       <c r="C50" s="104"/>
       <c r="D50" s="256">
         <v>25613.279999999999</v>
@@ -4074,24 +4077,24 @@
     </row>
     <row r="51" spans="1:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="365" t="s">
-        <v>476</v>
-      </c>
-      <c r="B51" s="369"/>
+        <v>475</v>
+      </c>
+      <c r="B51" s="393"/>
       <c r="C51" s="104"/>
       <c r="D51" s="256">
         <v>97574.399999999994</v>
       </c>
       <c r="E51" s="31" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F51" s="32"/>
       <c r="G51" s="32"/>
     </row>
     <row r="52" spans="1:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="365" t="s">
-        <v>452</v>
-      </c>
-      <c r="B52" s="369"/>
+        <v>451</v>
+      </c>
+      <c r="B52" s="393"/>
       <c r="C52" s="104"/>
       <c r="D52" s="256">
         <v>114432.12</v>
@@ -4117,7 +4120,7 @@
     </row>
     <row r="54" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="365" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B54" s="366"/>
       <c r="C54" s="105"/>
@@ -4125,14 +4128,14 @@
         <v>6300000</v>
       </c>
       <c r="E54" s="364" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F54" s="32"/>
       <c r="G54" s="32"/>
     </row>
     <row r="55" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="365" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B55" s="366"/>
       <c r="C55" s="105"/>
@@ -4140,7 +4143,7 @@
         <v>228690</v>
       </c>
       <c r="E55" s="31" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F55" s="32"/>
       <c r="G55" s="32"/>
@@ -4162,7 +4165,7 @@
     </row>
     <row r="57" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="365" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B57" s="366"/>
       <c r="C57" s="105"/>
@@ -4170,7 +4173,7 @@
         <v>1899700</v>
       </c>
       <c r="E57" s="31" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F57" s="32"/>
       <c r="G57" s="32"/>
@@ -4185,14 +4188,14 @@
         <v>943800</v>
       </c>
       <c r="E58" s="31" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F58" s="32"/>
       <c r="G58" s="32"/>
     </row>
     <row r="59" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="365" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B59" s="366"/>
       <c r="C59" s="105"/>
@@ -4205,7 +4208,7 @@
     </row>
     <row r="60" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="365" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B60" s="366"/>
       <c r="C60" s="105"/>
@@ -4213,14 +4216,14 @@
         <v>820380</v>
       </c>
       <c r="E60" s="80" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F60" s="32"/>
       <c r="G60" s="32"/>
     </row>
     <row r="61" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="365" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B61" s="366"/>
       <c r="C61" s="105"/>
@@ -4228,14 +4231,14 @@
         <v>110000</v>
       </c>
       <c r="E61" s="80" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F61" s="32"/>
       <c r="G61" s="32"/>
     </row>
     <row r="62" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="365" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B62" s="366"/>
       <c r="C62" s="105"/>
@@ -4243,14 +4246,14 @@
         <v>110000</v>
       </c>
       <c r="E62" s="80" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F62" s="32"/>
       <c r="G62" s="32"/>
     </row>
     <row r="63" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="365" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B63" s="366"/>
       <c r="C63" s="105"/>
@@ -4258,7 +4261,7 @@
         <v>220000</v>
       </c>
       <c r="E63" s="80" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F63" s="32"/>
       <c r="G63" s="32"/>
@@ -4295,7 +4298,7 @@
     </row>
     <row r="66" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="365" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B66" s="366"/>
       <c r="C66" s="105"/>
@@ -4310,7 +4313,7 @@
     </row>
     <row r="67" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="365" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B67" s="366"/>
       <c r="C67" s="105"/>
@@ -4325,7 +4328,7 @@
     </row>
     <row r="68" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="365" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B68" s="366"/>
       <c r="C68" s="24"/>
@@ -4333,7 +4336,7 @@
         <v>2459883</v>
       </c>
       <c r="E68" s="80" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F68" s="32"/>
       <c r="G68" s="277"/>
@@ -4366,7 +4369,7 @@
     </row>
     <row r="71" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="365" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B71" s="366"/>
       <c r="C71" s="24"/>
@@ -4374,29 +4377,29 @@
         <v>1500000</v>
       </c>
       <c r="E71" s="81" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F71" s="32"/>
       <c r="G71" s="32"/>
     </row>
     <row r="72" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="365" t="s">
-        <v>477</v>
-      </c>
-      <c r="B72" s="369"/>
+        <v>476</v>
+      </c>
+      <c r="B72" s="393"/>
       <c r="C72" s="366"/>
       <c r="D72" s="360">
         <v>750000</v>
       </c>
       <c r="E72" s="81" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F72" s="32"/>
       <c r="G72" s="32"/>
     </row>
     <row r="73" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="365" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B73" s="366"/>
       <c r="C73" s="24"/>
@@ -4404,14 +4407,14 @@
         <v>3600000</v>
       </c>
       <c r="E73" s="81" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F73" s="32"/>
       <c r="G73" s="32"/>
     </row>
     <row r="74" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="365" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B74" s="366"/>
       <c r="C74" s="101"/>
@@ -4419,14 +4422,14 @@
         <v>904475</v>
       </c>
       <c r="E74" s="146" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F74" s="277"/>
       <c r="G74" s="32"/>
     </row>
     <row r="75" spans="1:8" ht="52.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="365" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B75" s="366"/>
       <c r="C75" s="101"/>
@@ -4434,14 +4437,14 @@
         <v>188854.26</v>
       </c>
       <c r="E75" s="146" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F75" s="277"/>
       <c r="G75" s="32"/>
     </row>
     <row r="76" spans="1:8" ht="52.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="365" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B76" s="366"/>
       <c r="C76" s="101"/>
@@ -4449,14 +4452,14 @@
         <v>41000</v>
       </c>
       <c r="E76" s="146" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F76" s="277"/>
       <c r="G76" s="32"/>
     </row>
     <row r="77" spans="1:8" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="365" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B77" s="366"/>
       <c r="C77" s="101"/>
@@ -4464,14 +4467,14 @@
         <v>324000</v>
       </c>
       <c r="E77" s="146" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F77" s="277"/>
       <c r="G77" s="32"/>
     </row>
     <row r="78" spans="1:8" ht="31.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="237" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B78" s="269"/>
       <c r="C78" s="101"/>
@@ -4479,14 +4482,14 @@
         <v>62800</v>
       </c>
       <c r="E78" s="146" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F78" s="32"/>
       <c r="G78" s="32"/>
     </row>
     <row r="79" spans="1:8" ht="31.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="237" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B79" s="269"/>
       <c r="C79" s="101"/>
@@ -4494,14 +4497,14 @@
         <v>103600</v>
       </c>
       <c r="E79" s="146" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F79" s="32"/>
       <c r="G79" s="32"/>
     </row>
     <row r="80" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="365" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B80" s="366"/>
       <c r="C80" s="101"/>
@@ -4509,14 +4512,14 @@
         <v>21660</v>
       </c>
       <c r="E80" s="146" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F80" s="32"/>
       <c r="G80" s="32"/>
     </row>
     <row r="81" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="365" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B81" s="366"/>
       <c r="C81" s="101"/>
@@ -4524,16 +4527,16 @@
         <v>11610</v>
       </c>
       <c r="E81" s="146" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F81" s="277"/>
       <c r="G81" s="32"/>
     </row>
     <row r="82" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="367" t="s">
-        <v>445</v>
-      </c>
-      <c r="B82" s="368"/>
+      <c r="A82" s="371" t="s">
+        <v>444</v>
+      </c>
+      <c r="B82" s="372"/>
       <c r="C82" s="101"/>
       <c r="D82" s="360">
         <v>270185</v>
@@ -4544,7 +4547,7 @@
     </row>
     <row r="83" spans="1:7" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="365" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B83" s="366"/>
       <c r="C83" s="101"/>
@@ -4557,7 +4560,7 @@
     </row>
     <row r="84" spans="1:7" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="365" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B84" s="366"/>
       <c r="C84" s="101"/>
@@ -4570,7 +4573,7 @@
     </row>
     <row r="85" spans="1:7" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="365" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B85" s="366"/>
       <c r="C85" s="101"/>
@@ -4578,14 +4581,14 @@
         <v>1778700</v>
       </c>
       <c r="E85" s="88" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F85" s="277"/>
       <c r="G85" s="32"/>
     </row>
     <row r="86" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="365" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B86" s="366"/>
       <c r="C86" s="101"/>
@@ -4593,14 +4596,14 @@
         <v>175329</v>
       </c>
       <c r="E86" s="88" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F86" s="32"/>
       <c r="G86" s="32"/>
     </row>
     <row r="87" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="365" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B87" s="366"/>
       <c r="C87" s="101"/>
@@ -4613,7 +4616,7 @@
     </row>
     <row r="88" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="365" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B88" s="366"/>
       <c r="C88" s="101"/>
@@ -4621,14 +4624,14 @@
         <v>253193.5</v>
       </c>
       <c r="E88" s="88" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F88" s="32"/>
       <c r="G88" s="32"/>
     </row>
     <row r="89" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="365" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B89" s="366"/>
       <c r="C89" s="101"/>
@@ -4636,14 +4639,14 @@
         <v>57542.45</v>
       </c>
       <c r="E89" s="88" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F89" s="32"/>
       <c r="G89" s="32"/>
     </row>
     <row r="90" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="365" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B90" s="366"/>
       <c r="C90" s="101"/>
@@ -4651,14 +4654,14 @@
         <v>27888.333999999999</v>
       </c>
       <c r="E90" s="88" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F90" s="32"/>
       <c r="G90" s="32"/>
     </row>
     <row r="91" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="365" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B91" s="366"/>
       <c r="C91" s="101"/>
@@ -4666,14 +4669,14 @@
         <v>18600</v>
       </c>
       <c r="E91" s="88" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F91" s="32"/>
       <c r="G91" s="32"/>
     </row>
     <row r="92" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="365" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B92" s="366"/>
       <c r="C92" s="101"/>
@@ -4681,14 +4684,14 @@
         <v>1154830.69</v>
       </c>
       <c r="E92" s="88" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F92" s="32"/>
       <c r="G92" s="32"/>
     </row>
     <row r="93" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="365" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B93" s="366"/>
       <c r="C93" s="101"/>
@@ -4696,14 +4699,14 @@
         <v>1250000</v>
       </c>
       <c r="E93" s="88" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F93" s="32"/>
       <c r="G93" s="32"/>
     </row>
     <row r="94" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="365" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B94" s="366"/>
       <c r="C94" s="101"/>
@@ -4711,14 +4714,14 @@
         <v>1250000</v>
       </c>
       <c r="E94" s="88" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F94" s="32"/>
       <c r="G94" s="32"/>
     </row>
     <row r="95" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="365" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B95" s="366"/>
       <c r="C95" s="101"/>
@@ -4726,7 +4729,7 @@
         <v>750000</v>
       </c>
       <c r="E95" s="88" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F95" s="32"/>
       <c r="G95" s="32"/>
@@ -4741,7 +4744,7 @@
         <v>350000</v>
       </c>
       <c r="E96" s="81" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F96" s="32"/>
       <c r="G96" s="32"/>
@@ -4773,7 +4776,7 @@
     </row>
     <row r="99" spans="1:7" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="365" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B99" s="366"/>
       <c r="C99" s="24"/>
@@ -4788,7 +4791,7 @@
     </row>
     <row r="100" spans="1:7" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="365" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B100" s="366"/>
       <c r="C100" s="24"/>
@@ -4991,70 +4994,70 @@
       <c r="G115" s="32"/>
     </row>
     <row r="116" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="397" t="s">
-        <v>447</v>
-      </c>
-      <c r="B116" s="398"/>
+      <c r="A116" s="367" t="s">
+        <v>446</v>
+      </c>
+      <c r="B116" s="368"/>
       <c r="C116" s="24"/>
       <c r="D116" s="256">
         <v>1213387.58</v>
       </c>
       <c r="E116" s="81" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F116" s="32"/>
       <c r="G116" s="32"/>
     </row>
     <row r="117" spans="1:7" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="397" t="s">
-        <v>448</v>
-      </c>
-      <c r="B117" s="398"/>
+      <c r="A117" s="367" t="s">
+        <v>447</v>
+      </c>
+      <c r="B117" s="368"/>
       <c r="C117" s="24"/>
       <c r="D117" s="256">
         <v>433890.06</v>
       </c>
       <c r="E117" s="81" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F117" s="32"/>
       <c r="G117" s="32"/>
     </row>
     <row r="118" spans="1:7" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="397" t="s">
-        <v>449</v>
-      </c>
-      <c r="B118" s="398"/>
+      <c r="A118" s="367" t="s">
+        <v>448</v>
+      </c>
+      <c r="B118" s="368"/>
       <c r="C118" s="24"/>
       <c r="D118" s="256">
         <v>118075.67</v>
       </c>
       <c r="E118" s="81" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F118" s="32"/>
       <c r="G118" s="32"/>
     </row>
     <row r="119" spans="1:7" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="397" t="s">
-        <v>450</v>
-      </c>
-      <c r="B119" s="398"/>
+      <c r="A119" s="367" t="s">
+        <v>449</v>
+      </c>
+      <c r="B119" s="368"/>
       <c r="C119" s="24"/>
       <c r="D119" s="256">
         <v>87899.24</v>
       </c>
       <c r="E119" s="81" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F119" s="32"/>
       <c r="G119" s="32"/>
     </row>
     <row r="120" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="397" t="s">
+      <c r="A120" s="367" t="s">
         <v>189</v>
       </c>
-      <c r="B120" s="398"/>
+      <c r="B120" s="368"/>
       <c r="C120" s="24"/>
       <c r="D120" s="204">
         <v>27930.75</v>
@@ -5067,10 +5070,10 @@
       <c r="G120" s="32"/>
     </row>
     <row r="121" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="397" t="s">
+      <c r="A121" s="367" t="s">
         <v>300</v>
       </c>
-      <c r="B121" s="398"/>
+      <c r="B121" s="368"/>
       <c r="C121" s="24"/>
       <c r="D121" s="204">
         <v>6678</v>
@@ -5118,25 +5121,25 @@
       <c r="G124" s="32"/>
     </row>
     <row r="125" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="397" t="s">
-        <v>438</v>
-      </c>
-      <c r="B125" s="398"/>
+      <c r="A125" s="367" t="s">
+        <v>437</v>
+      </c>
+      <c r="B125" s="368"/>
       <c r="C125" s="24"/>
       <c r="D125" s="359">
         <v>17995434.600000001</v>
       </c>
       <c r="E125" s="80" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F125" s="32"/>
       <c r="G125" s="32"/>
     </row>
     <row r="126" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="397" t="s">
+      <c r="A126" s="367" t="s">
         <v>346</v>
       </c>
-      <c r="B126" s="398"/>
+      <c r="B126" s="368"/>
       <c r="C126" s="24"/>
       <c r="D126" s="281">
         <v>380000</v>
@@ -5149,7 +5152,7 @@
     </row>
     <row r="127" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="365" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B127" s="366"/>
       <c r="C127" s="24"/>
@@ -5157,37 +5160,37 @@
         <v>1443530</v>
       </c>
       <c r="E127" s="146" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F127" s="32"/>
       <c r="G127" s="32"/>
     </row>
     <row r="128" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="367" t="s">
-        <v>417</v>
-      </c>
-      <c r="B128" s="368"/>
+      <c r="A128" s="371" t="s">
+        <v>416</v>
+      </c>
+      <c r="B128" s="372"/>
       <c r="C128" s="24"/>
       <c r="D128" s="359">
         <v>8064666.6699999999</v>
       </c>
       <c r="E128" s="146" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F128" s="32"/>
       <c r="G128" s="32"/>
     </row>
     <row r="129" spans="1:7" ht="43.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A129" s="367" t="s">
-        <v>417</v>
-      </c>
-      <c r="B129" s="368"/>
+      <c r="A129" s="371" t="s">
+        <v>416</v>
+      </c>
+      <c r="B129" s="372"/>
       <c r="C129" s="101"/>
       <c r="D129" s="359">
         <v>1071600</v>
       </c>
       <c r="E129" s="146" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F129" s="32"/>
       <c r="G129" s="32"/>
@@ -5268,10 +5271,10 @@
       <c r="G136" s="32"/>
     </row>
     <row r="137" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="396" t="s">
-        <v>413</v>
-      </c>
-      <c r="B137" s="396"/>
+      <c r="A137" s="370" t="s">
+        <v>412</v>
+      </c>
+      <c r="B137" s="370"/>
       <c r="C137" s="24"/>
       <c r="D137" s="256">
         <f>2104581-1520000</f>
@@ -5286,7 +5289,7 @@
     </row>
     <row r="138" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="365" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B138" s="366"/>
       <c r="C138" s="24"/>
@@ -5302,7 +5305,7 @@
     </row>
     <row r="139" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="365" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B139" s="366"/>
       <c r="C139" s="24"/>
@@ -5433,24 +5436,24 @@
       <c r="E151" s="32"/>
     </row>
     <row r="152" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="403" t="s">
-        <v>377</v>
-      </c>
-      <c r="B152" s="404"/>
+      <c r="A152" s="377" t="s">
+        <v>376</v>
+      </c>
+      <c r="B152" s="378"/>
       <c r="C152" s="32"/>
       <c r="D152" s="32"/>
       <c r="E152" s="32"/>
     </row>
     <row r="153" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="405"/>
-      <c r="B153" s="406"/>
+      <c r="A153" s="379"/>
+      <c r="B153" s="380"/>
       <c r="C153" s="32"/>
       <c r="D153" s="32"/>
       <c r="E153" s="32"/>
     </row>
     <row r="154" spans="1:5" ht="54.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A154" s="407"/>
-      <c r="B154" s="408"/>
+      <c r="A154" s="381"/>
+      <c r="B154" s="382"/>
       <c r="C154" s="32"/>
       <c r="D154" s="32"/>
       <c r="E154" s="32"/>
@@ -5643,10 +5646,10 @@
       <c r="F172" s="77"/>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A173" s="401" t="s">
+      <c r="A173" s="375" t="s">
         <v>329</v>
       </c>
-      <c r="B173" s="402"/>
+      <c r="B173" s="376"/>
       <c r="C173" s="6"/>
       <c r="D173" s="13"/>
       <c r="E173" s="36"/>
@@ -5715,10 +5718,10 @@
       <c r="F179" s="77"/>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A180" s="399" t="s">
+      <c r="A180" s="373" t="s">
         <v>292</v>
       </c>
-      <c r="B180" s="400"/>
+      <c r="B180" s="374"/>
       <c r="C180" s="6"/>
       <c r="D180" s="13"/>
       <c r="E180" s="36"/>
@@ -5827,7 +5830,7 @@
     </row>
     <row r="190" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="91" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B190" s="256">
         <v>-8350</v>
@@ -6024,16 +6027,16 @@
       <c r="F202" s="37"/>
     </row>
     <row r="203" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A203" s="395" t="s">
+      <c r="A203" s="369" t="s">
         <v>17</v>
       </c>
-      <c r="B203" s="395"/>
-      <c r="C203" s="395"/>
+      <c r="B203" s="369"/>
+      <c r="C203" s="369"/>
     </row>
     <row r="204" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A204" s="395"/>
-      <c r="B204" s="395"/>
-      <c r="C204" s="395"/>
+      <c r="A204" s="369"/>
+      <c r="B204" s="369"/>
+      <c r="C204" s="369"/>
     </row>
     <row r="205" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="65"/>
@@ -6060,6 +6063,76 @@
     </row>
   </sheetData>
   <mergeCells count="86">
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A1:A8"/>
+    <mergeCell ref="A10:E12"/>
+    <mergeCell ref="A15:E18"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A203:C204"/>
+    <mergeCell ref="A137:B137"/>
+    <mergeCell ref="A129:B129"/>
+    <mergeCell ref="A125:B125"/>
+    <mergeCell ref="A180:B180"/>
+    <mergeCell ref="A140:B140"/>
+    <mergeCell ref="A173:B173"/>
+    <mergeCell ref="A152:B154"/>
+    <mergeCell ref="A139:B139"/>
+    <mergeCell ref="A138:B138"/>
+    <mergeCell ref="A127:B127"/>
+    <mergeCell ref="A126:B126"/>
+    <mergeCell ref="A128:B128"/>
+    <mergeCell ref="A121:B121"/>
+    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="A120:B120"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="A114:B114"/>
+    <mergeCell ref="A115:B115"/>
+    <mergeCell ref="A112:B112"/>
+    <mergeCell ref="A118:B118"/>
+    <mergeCell ref="A117:B117"/>
+    <mergeCell ref="A119:B119"/>
+    <mergeCell ref="A100:B100"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="A73:B73"/>
     <mergeCell ref="A67:B67"/>
@@ -6076,76 +6149,6 @@
     <mergeCell ref="A63:B63"/>
     <mergeCell ref="A68:B68"/>
     <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A121:B121"/>
-    <mergeCell ref="A116:B116"/>
-    <mergeCell ref="A120:B120"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="A114:B114"/>
-    <mergeCell ref="A115:B115"/>
-    <mergeCell ref="A112:B112"/>
-    <mergeCell ref="A118:B118"/>
-    <mergeCell ref="A117:B117"/>
-    <mergeCell ref="A119:B119"/>
-    <mergeCell ref="A100:B100"/>
-    <mergeCell ref="A203:C204"/>
-    <mergeCell ref="A137:B137"/>
-    <mergeCell ref="A129:B129"/>
-    <mergeCell ref="A125:B125"/>
-    <mergeCell ref="A180:B180"/>
-    <mergeCell ref="A140:B140"/>
-    <mergeCell ref="A173:B173"/>
-    <mergeCell ref="A152:B154"/>
-    <mergeCell ref="A139:B139"/>
-    <mergeCell ref="A138:B138"/>
-    <mergeCell ref="A127:B127"/>
-    <mergeCell ref="A126:B126"/>
-    <mergeCell ref="A128:B128"/>
-    <mergeCell ref="A10:E12"/>
-    <mergeCell ref="A15:E18"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A1:A8"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A95:B95"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A66:B66"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="115" orientation="portrait" r:id="rId1"/>
@@ -6185,27 +6188,27 @@
     <row r="1" spans="1:24" ht="189.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="420" t="s">
+      <c r="C1" s="422" t="s">
         <v>335</v>
       </c>
-      <c r="D1" s="421"/>
-      <c r="E1" s="421"/>
-      <c r="F1" s="421"/>
-      <c r="G1" s="421"/>
-      <c r="H1" s="421"/>
-      <c r="I1" s="421"/>
-      <c r="J1" s="421"/>
-      <c r="K1" s="421"/>
-      <c r="L1" s="421"/>
+      <c r="D1" s="423"/>
+      <c r="E1" s="423"/>
+      <c r="F1" s="423"/>
+      <c r="G1" s="423"/>
+      <c r="H1" s="423"/>
+      <c r="I1" s="423"/>
+      <c r="J1" s="423"/>
+      <c r="K1" s="423"/>
+      <c r="L1" s="423"/>
       <c r="M1" s="145"/>
-      <c r="N1" s="422" t="s">
+      <c r="N1" s="424" t="s">
         <v>312</v>
       </c>
-      <c r="O1" s="422"/>
-      <c r="P1" s="417">
+      <c r="O1" s="424"/>
+      <c r="P1" s="419">
         <v>30000000</v>
       </c>
-      <c r="Q1" s="417"/>
+      <c r="Q1" s="419"/>
       <c r="R1" s="168"/>
       <c r="S1" s="4"/>
       <c r="T1" s="2"/>
@@ -6219,11 +6222,11 @@
     <row r="2" spans="1:24" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="419" t="s">
+      <c r="C2" s="421" t="s">
         <v>226</v>
       </c>
-      <c r="D2" s="419"/>
-      <c r="E2" s="419"/>
+      <c r="D2" s="421"/>
+      <c r="E2" s="421"/>
       <c r="F2" s="145"/>
       <c r="G2" s="416">
         <f>X2</f>
@@ -6244,10 +6247,10 @@
         <v>260</v>
       </c>
       <c r="O2" s="230"/>
-      <c r="P2" s="418">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="418"/>
+      <c r="P2" s="420">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="420"/>
       <c r="R2" s="169"/>
       <c r="T2" s="2"/>
       <c r="U2" t="s">
@@ -6259,112 +6262,112 @@
       </c>
     </row>
     <row r="3" spans="1:24" ht="91.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="427" t="str">
+      <c r="A3" s="429" t="str">
         <f>"ATENCIÓN: Si usted abona antes del " &amp; TEXT(RESUMEN!A10,"dd/mm/yyyy") &amp; ", deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste."</f>
         <v>ATENCIÓN: Si usted abona antes del Primer Vencimiento:  17/07, deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste.</v>
       </c>
-      <c r="B3" s="428"/>
-      <c r="C3" s="428"/>
-      <c r="D3" s="428"/>
-      <c r="E3" s="428"/>
-      <c r="F3" s="428"/>
-      <c r="G3" s="428"/>
-      <c r="H3" s="428"/>
-      <c r="I3" s="428"/>
-      <c r="J3" s="428"/>
-      <c r="K3" s="428"/>
-      <c r="L3" s="428"/>
-      <c r="M3" s="428"/>
-      <c r="N3" s="428"/>
-      <c r="O3" s="428"/>
-      <c r="P3" s="428"/>
-      <c r="Q3" s="428"/>
-      <c r="R3" s="428"/>
-      <c r="S3" s="428"/>
-      <c r="T3" s="429"/>
+      <c r="B3" s="430"/>
+      <c r="C3" s="430"/>
+      <c r="D3" s="430"/>
+      <c r="E3" s="430"/>
+      <c r="F3" s="430"/>
+      <c r="G3" s="430"/>
+      <c r="H3" s="430"/>
+      <c r="I3" s="430"/>
+      <c r="J3" s="430"/>
+      <c r="K3" s="430"/>
+      <c r="L3" s="430"/>
+      <c r="M3" s="430"/>
+      <c r="N3" s="430"/>
+      <c r="O3" s="430"/>
+      <c r="P3" s="430"/>
+      <c r="Q3" s="430"/>
+      <c r="R3" s="430"/>
+      <c r="S3" s="430"/>
+      <c r="T3" s="431"/>
       <c r="X3" s="39"/>
     </row>
     <row r="4" spans="1:24" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="430" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="432" t="s">
+      <c r="A4" s="432" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="434" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="432" t="s">
+      <c r="C4" s="434" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="432" t="s">
+      <c r="D4" s="434" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="409" t="s">
+      <c r="E4" s="417" t="s">
         <v>181</v>
       </c>
-      <c r="F4" s="432" t="s">
+      <c r="F4" s="434" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="434" t="s">
+      <c r="G4" s="436" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="409" t="s">
+      <c r="H4" s="417" t="s">
         <v>232</v>
       </c>
-      <c r="I4" s="409" t="s">
+      <c r="I4" s="417" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="409"/>
-      <c r="K4" s="409" t="s">
+      <c r="J4" s="417"/>
+      <c r="K4" s="417" t="s">
         <v>182</v>
       </c>
-      <c r="L4" s="409" t="s">
+      <c r="L4" s="417" t="s">
         <v>146</v>
       </c>
-      <c r="M4" s="409" t="s">
+      <c r="M4" s="417" t="s">
         <v>184</v>
       </c>
-      <c r="N4" s="409" t="s">
+      <c r="N4" s="417" t="s">
         <v>183</v>
       </c>
-      <c r="O4" s="409" t="s">
+      <c r="O4" s="417" t="s">
         <v>322</v>
       </c>
-      <c r="P4" s="423" t="s">
+      <c r="P4" s="425" t="s">
         <v>320</v>
       </c>
-      <c r="Q4" s="424"/>
-      <c r="R4" s="423" t="s">
+      <c r="Q4" s="426"/>
+      <c r="R4" s="425" t="s">
         <v>315</v>
       </c>
-      <c r="S4" s="424"/>
-      <c r="T4" s="409" t="s">
+      <c r="S4" s="426"/>
+      <c r="T4" s="417" t="s">
         <v>258</v>
       </c>
       <c r="U4" s="13"/>
     </row>
     <row r="5" spans="1:24" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="431"/>
-      <c r="B5" s="433"/>
-      <c r="C5" s="433"/>
-      <c r="D5" s="433"/>
-      <c r="E5" s="410"/>
-      <c r="F5" s="433"/>
-      <c r="G5" s="435"/>
-      <c r="H5" s="410"/>
-      <c r="I5" s="410"/>
-      <c r="J5" s="410"/>
-      <c r="K5" s="410"/>
-      <c r="L5" s="410"/>
-      <c r="M5" s="410"/>
-      <c r="N5" s="410"/>
-      <c r="O5" s="410"/>
-      <c r="P5" s="425" t="str">
+      <c r="A5" s="433"/>
+      <c r="B5" s="435"/>
+      <c r="C5" s="435"/>
+      <c r="D5" s="435"/>
+      <c r="E5" s="418"/>
+      <c r="F5" s="435"/>
+      <c r="G5" s="437"/>
+      <c r="H5" s="418"/>
+      <c r="I5" s="418"/>
+      <c r="J5" s="418"/>
+      <c r="K5" s="418"/>
+      <c r="L5" s="418"/>
+      <c r="M5" s="418"/>
+      <c r="N5" s="418"/>
+      <c r="O5" s="418"/>
+      <c r="P5" s="427" t="str">
         <f>RESUMEN!A10</f>
         <v>Primer Vencimiento:  17/07</v>
       </c>
-      <c r="Q5" s="426"/>
-      <c r="R5" s="425"/>
-      <c r="S5" s="426"/>
-      <c r="T5" s="410"/>
+      <c r="Q5" s="428"/>
+      <c r="R5" s="427"/>
+      <c r="S5" s="428"/>
+      <c r="T5" s="418"/>
     </row>
     <row r="6" spans="1:24" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="188"/>
@@ -6418,11 +6421,11 @@
       <c r="O6" s="190">
         <v>0</v>
       </c>
-      <c r="P6" s="411">
+      <c r="P6" s="438">
         <f t="shared" ref="P6:P37" si="2">ROUND(SUM(G6:O6),0) + S6</f>
         <v>759748.01</v>
       </c>
-      <c r="Q6" s="412"/>
+      <c r="Q6" s="439"/>
       <c r="R6" s="232">
         <f t="shared" ref="R6:R37" si="3">ROUND(P6+P6*3.033%,0) + S6</f>
         <v>782791.01</v>
@@ -6489,11 +6492,11 @@
       <c r="O7" s="190">
         <v>0</v>
       </c>
-      <c r="P7" s="413">
+      <c r="P7" s="440">
         <f t="shared" si="2"/>
         <v>1990555.02</v>
       </c>
-      <c r="Q7" s="414"/>
+      <c r="Q7" s="441"/>
       <c r="R7" s="232">
         <f t="shared" si="3"/>
         <v>2050929.02</v>
@@ -6559,11 +6562,11 @@
       <c r="O8" s="190">
         <v>0</v>
       </c>
-      <c r="P8" s="415">
+      <c r="P8" s="409">
         <f t="shared" si="2"/>
         <v>737404.03</v>
       </c>
-      <c r="Q8" s="415"/>
+      <c r="Q8" s="409"/>
       <c r="R8" s="232">
         <f t="shared" si="3"/>
         <v>759769.03</v>
@@ -6630,11 +6633,11 @@
       <c r="O9" s="190">
         <v>0</v>
       </c>
-      <c r="P9" s="415">
+      <c r="P9" s="409">
         <f t="shared" si="2"/>
         <v>1559335.04</v>
       </c>
-      <c r="Q9" s="415"/>
+      <c r="Q9" s="409"/>
       <c r="R9" s="232">
         <f t="shared" si="3"/>
         <v>1606630.04</v>
@@ -6705,11 +6708,11 @@
       <c r="O10" s="190">
         <v>0</v>
       </c>
-      <c r="P10" s="415">
+      <c r="P10" s="409">
         <f t="shared" si="2"/>
         <v>767816.05</v>
       </c>
-      <c r="Q10" s="415"/>
+      <c r="Q10" s="409"/>
       <c r="R10" s="232">
         <f t="shared" si="3"/>
         <v>791104.05</v>
@@ -6777,11 +6780,11 @@
       <c r="O11" s="190">
         <v>0</v>
       </c>
-      <c r="P11" s="415">
+      <c r="P11" s="409">
         <f t="shared" si="2"/>
         <v>751681.06</v>
       </c>
-      <c r="Q11" s="415"/>
+      <c r="Q11" s="409"/>
       <c r="R11" s="232">
         <f t="shared" si="3"/>
         <v>774480.06</v>
@@ -6851,11 +6854,11 @@
         <f>I12/2</f>
         <v>173453.32242800001</v>
       </c>
-      <c r="P12" s="415">
+      <c r="P12" s="409">
         <f t="shared" si="2"/>
         <v>908854.07</v>
       </c>
-      <c r="Q12" s="415"/>
+      <c r="Q12" s="409"/>
       <c r="R12" s="232">
         <f t="shared" si="3"/>
         <v>936420.07</v>
@@ -6924,11 +6927,11 @@
       <c r="O13" s="190">
         <v>0</v>
       </c>
-      <c r="P13" s="415">
+      <c r="P13" s="409">
         <f t="shared" si="2"/>
         <v>744528.08</v>
       </c>
-      <c r="Q13" s="415"/>
+      <c r="Q13" s="409"/>
       <c r="R13" s="232">
         <f t="shared" si="3"/>
         <v>767110.08</v>
@@ -6998,11 +7001,11 @@
       <c r="O14" s="190">
         <v>0</v>
       </c>
-      <c r="P14" s="415">
+      <c r="P14" s="409">
         <f t="shared" si="2"/>
         <v>282288.09000000003</v>
       </c>
-      <c r="Q14" s="415"/>
+      <c r="Q14" s="409"/>
       <c r="R14" s="232">
         <f t="shared" si="3"/>
         <v>290850.09000000003</v>
@@ -7069,11 +7072,11 @@
       <c r="O15" s="190">
         <v>0</v>
       </c>
-      <c r="P15" s="415">
+      <c r="P15" s="409">
         <f t="shared" si="2"/>
         <v>767816.1</v>
       </c>
-      <c r="Q15" s="415"/>
+      <c r="Q15" s="409"/>
       <c r="R15" s="232">
         <f t="shared" si="3"/>
         <v>791104.1</v>
@@ -7142,11 +7145,11 @@
       <c r="O16" s="190">
         <v>0</v>
       </c>
-      <c r="P16" s="415">
+      <c r="P16" s="409">
         <f t="shared" si="2"/>
         <v>745234.11</v>
       </c>
-      <c r="Q16" s="415"/>
+      <c r="Q16" s="409"/>
       <c r="R16" s="232">
         <f t="shared" si="3"/>
         <v>767837.11</v>
@@ -7215,11 +7218,11 @@
       <c r="O17" s="190">
         <v>0</v>
       </c>
-      <c r="P17" s="415">
+      <c r="P17" s="409">
         <f t="shared" si="2"/>
         <v>4296506.12</v>
       </c>
-      <c r="Q17" s="415"/>
+      <c r="Q17" s="409"/>
       <c r="R17" s="232">
         <f t="shared" si="3"/>
         <v>4426819.12</v>
@@ -7289,11 +7292,11 @@
       <c r="O18" s="190">
         <v>0</v>
       </c>
-      <c r="P18" s="415">
+      <c r="P18" s="409">
         <f t="shared" si="2"/>
         <v>759748.13</v>
       </c>
-      <c r="Q18" s="415"/>
+      <c r="Q18" s="409"/>
       <c r="R18" s="232">
         <f t="shared" si="3"/>
         <v>782791.13</v>
@@ -7360,11 +7363,11 @@
       <c r="O19" s="190">
         <v>0</v>
       </c>
-      <c r="P19" s="415">
+      <c r="P19" s="409">
         <f t="shared" si="2"/>
         <v>767456.14</v>
       </c>
-      <c r="Q19" s="415"/>
+      <c r="Q19" s="409"/>
       <c r="R19" s="232">
         <f t="shared" si="3"/>
         <v>790733.14</v>
@@ -7434,11 +7437,11 @@
       <c r="O20" s="190">
         <v>0</v>
       </c>
-      <c r="P20" s="415">
+      <c r="P20" s="409">
         <f t="shared" si="2"/>
         <v>743613.15</v>
       </c>
-      <c r="Q20" s="415"/>
+      <c r="Q20" s="409"/>
       <c r="R20" s="232">
         <f t="shared" si="3"/>
         <v>766167.15</v>
@@ -7508,11 +7511,11 @@
       <c r="O21" s="284">
         <v>97321.42</v>
       </c>
-      <c r="P21" s="415">
+      <c r="P21" s="409">
         <f t="shared" si="2"/>
         <v>857070.16</v>
       </c>
-      <c r="Q21" s="415"/>
+      <c r="Q21" s="409"/>
       <c r="R21" s="232">
         <f t="shared" si="3"/>
         <v>883065.16</v>
@@ -7579,11 +7582,11 @@
       <c r="O22" s="190">
         <v>0</v>
       </c>
-      <c r="P22" s="415">
+      <c r="P22" s="409">
         <f t="shared" si="2"/>
         <v>1460199.17</v>
       </c>
-      <c r="Q22" s="415"/>
+      <c r="Q22" s="409"/>
       <c r="R22" s="232">
         <f t="shared" si="3"/>
         <v>1504487.17</v>
@@ -7653,11 +7656,11 @@
       <c r="O23" s="190">
         <v>0</v>
       </c>
-      <c r="P23" s="415">
+      <c r="P23" s="409">
         <f t="shared" si="2"/>
         <v>749748.18</v>
       </c>
-      <c r="Q23" s="415"/>
+      <c r="Q23" s="409"/>
       <c r="R23" s="232">
         <f t="shared" si="3"/>
         <v>772488.18</v>
@@ -7726,11 +7729,11 @@
       <c r="O24" s="190">
         <v>0</v>
       </c>
-      <c r="P24" s="415">
+      <c r="P24" s="409">
         <f t="shared" si="2"/>
         <v>745213.19</v>
       </c>
-      <c r="Q24" s="415"/>
+      <c r="Q24" s="409"/>
       <c r="R24" s="232">
         <f t="shared" si="3"/>
         <v>767816.19</v>
@@ -7797,11 +7800,11 @@
       <c r="O25" s="190">
         <v>0</v>
       </c>
-      <c r="P25" s="415">
+      <c r="P25" s="409">
         <f t="shared" si="2"/>
         <v>767816.2</v>
       </c>
-      <c r="Q25" s="415"/>
+      <c r="Q25" s="409"/>
       <c r="R25" s="232">
         <f t="shared" si="3"/>
         <v>791104.2</v>
@@ -7868,11 +7871,11 @@
       <c r="O26" s="190">
         <v>0</v>
       </c>
-      <c r="P26" s="415">
+      <c r="P26" s="409">
         <f t="shared" si="2"/>
         <v>767816.21</v>
       </c>
-      <c r="Q26" s="415"/>
+      <c r="Q26" s="409"/>
       <c r="R26" s="232">
         <f t="shared" si="3"/>
         <v>791104.21</v>
@@ -7944,11 +7947,11 @@
       <c r="O27" s="190">
         <v>0</v>
       </c>
-      <c r="P27" s="415">
+      <c r="P27" s="409">
         <f t="shared" si="2"/>
         <v>745234.22</v>
       </c>
-      <c r="Q27" s="415"/>
+      <c r="Q27" s="409"/>
       <c r="R27" s="232">
         <f t="shared" si="3"/>
         <v>767837.22</v>
@@ -8018,11 +8021,11 @@
       <c r="O28" s="190">
         <v>0</v>
       </c>
-      <c r="P28" s="415">
+      <c r="P28" s="409">
         <f t="shared" si="2"/>
         <v>767816.23</v>
       </c>
-      <c r="Q28" s="415"/>
+      <c r="Q28" s="409"/>
       <c r="R28" s="232">
         <f t="shared" si="3"/>
         <v>791104.23</v>
@@ -8091,11 +8094,11 @@
       <c r="O29" s="190">
         <v>0</v>
       </c>
-      <c r="P29" s="415">
+      <c r="P29" s="409">
         <f t="shared" si="2"/>
         <v>745213.24</v>
       </c>
-      <c r="Q29" s="415"/>
+      <c r="Q29" s="409"/>
       <c r="R29" s="232">
         <f t="shared" si="3"/>
         <v>767816.24</v>
@@ -8165,11 +8168,11 @@
       <c r="O30" s="190">
         <v>0</v>
       </c>
-      <c r="P30" s="415">
+      <c r="P30" s="409">
         <f t="shared" si="2"/>
         <v>775884.25</v>
       </c>
-      <c r="Q30" s="415"/>
+      <c r="Q30" s="409"/>
       <c r="R30" s="232">
         <f t="shared" si="3"/>
         <v>799417.25</v>
@@ -8239,11 +8242,11 @@
       <c r="O31" s="190">
         <v>0</v>
       </c>
-      <c r="P31" s="415">
+      <c r="P31" s="409">
         <f t="shared" si="2"/>
         <v>775884.26</v>
       </c>
-      <c r="Q31" s="415"/>
+      <c r="Q31" s="409"/>
       <c r="R31" s="232">
         <f t="shared" si="3"/>
         <v>799417.26</v>
@@ -8312,11 +8315,11 @@
       <c r="O32" s="190">
         <v>0</v>
       </c>
-      <c r="P32" s="415">
+      <c r="P32" s="409">
         <f t="shared" si="2"/>
         <v>775945.27</v>
       </c>
-      <c r="Q32" s="415"/>
+      <c r="Q32" s="409"/>
       <c r="R32" s="232">
         <f t="shared" si="3"/>
         <v>799480.27</v>
@@ -8382,11 +8385,11 @@
       <c r="O33" s="190">
         <v>0</v>
       </c>
-      <c r="P33" s="415">
+      <c r="P33" s="409">
         <f t="shared" si="2"/>
         <v>662471.28</v>
       </c>
-      <c r="Q33" s="415"/>
+      <c r="Q33" s="409"/>
       <c r="R33" s="232">
         <f t="shared" si="3"/>
         <v>682564.28</v>
@@ -8455,11 +8458,11 @@
       <c r="O34" s="190">
         <v>0</v>
       </c>
-      <c r="P34" s="415">
+      <c r="P34" s="409">
         <f t="shared" si="2"/>
         <v>752351.29</v>
       </c>
-      <c r="Q34" s="415"/>
+      <c r="Q34" s="409"/>
       <c r="R34" s="232">
         <f t="shared" si="3"/>
         <v>775170.29</v>
@@ -8528,11 +8531,11 @@
       <c r="O35" s="190">
         <v>0</v>
       </c>
-      <c r="P35" s="415">
+      <c r="P35" s="409">
         <f t="shared" si="2"/>
         <v>729574.3</v>
       </c>
-      <c r="Q35" s="415"/>
+      <c r="Q35" s="409"/>
       <c r="R35" s="232">
         <f t="shared" si="3"/>
         <v>751702.3</v>
@@ -8599,11 +8602,11 @@
       <c r="O36" s="190">
         <v>0</v>
       </c>
-      <c r="P36" s="415">
+      <c r="P36" s="409">
         <f t="shared" si="2"/>
         <v>825173.31</v>
       </c>
-      <c r="Q36" s="415"/>
+      <c r="Q36" s="409"/>
       <c r="R36" s="232">
         <f t="shared" si="3"/>
         <v>850201.31</v>
@@ -8673,11 +8676,11 @@
       <c r="O37" s="190">
         <v>0</v>
       </c>
-      <c r="P37" s="415">
+      <c r="P37" s="409">
         <f t="shared" si="2"/>
         <v>618437.31999999995</v>
       </c>
-      <c r="Q37" s="415"/>
+      <c r="Q37" s="409"/>
       <c r="R37" s="232">
         <f t="shared" si="3"/>
         <v>637195.31999999995</v>
@@ -8743,11 +8746,11 @@
       <c r="O38" s="190">
         <v>0</v>
       </c>
-      <c r="P38" s="415">
+      <c r="P38" s="409">
         <f t="shared" ref="P38:P69" si="14">ROUND(SUM(G38:O38),0) + S38</f>
         <v>751681.33</v>
       </c>
-      <c r="Q38" s="415"/>
+      <c r="Q38" s="409"/>
       <c r="R38" s="232">
         <f t="shared" ref="R38:R69" si="15">ROUND(P38+P38*3.033%,0) + S38</f>
         <v>774480.33</v>
@@ -8812,11 +8815,11 @@
       <c r="O39" s="190">
         <v>0</v>
       </c>
-      <c r="P39" s="415">
+      <c r="P39" s="409">
         <f t="shared" si="14"/>
         <v>650288.34</v>
       </c>
-      <c r="Q39" s="415"/>
+      <c r="Q39" s="409"/>
       <c r="R39" s="232">
         <f t="shared" si="15"/>
         <v>670012.34</v>
@@ -8887,11 +8890,11 @@
       <c r="O40" s="190">
         <v>0</v>
       </c>
-      <c r="P40" s="415">
+      <c r="P40" s="409">
         <f t="shared" si="14"/>
         <v>759748.35</v>
       </c>
-      <c r="Q40" s="415"/>
+      <c r="Q40" s="409"/>
       <c r="R40" s="232">
         <f t="shared" si="15"/>
         <v>782792.35</v>
@@ -8961,11 +8964,11 @@
       <c r="O41" s="190">
         <v>0</v>
       </c>
-      <c r="P41" s="415">
+      <c r="P41" s="409">
         <f t="shared" si="14"/>
         <v>1051082.3600000001</v>
       </c>
-      <c r="Q41" s="415"/>
+      <c r="Q41" s="409"/>
       <c r="R41" s="232">
         <f t="shared" si="15"/>
         <v>1082962.3600000001</v>
@@ -9033,11 +9036,11 @@
       <c r="O42" s="190">
         <v>0</v>
       </c>
-      <c r="P42" s="415">
+      <c r="P42" s="409">
         <f t="shared" si="14"/>
         <v>705348.37</v>
       </c>
-      <c r="Q42" s="415"/>
+      <c r="Q42" s="409"/>
       <c r="R42" s="232">
         <f t="shared" si="15"/>
         <v>726742.37</v>
@@ -9105,11 +9108,11 @@
       <c r="O43" s="190">
         <v>0</v>
       </c>
-      <c r="P43" s="415">
+      <c r="P43" s="409">
         <f t="shared" si="14"/>
         <v>724030.38</v>
       </c>
-      <c r="Q43" s="415"/>
+      <c r="Q43" s="409"/>
       <c r="R43" s="232">
         <f t="shared" si="15"/>
         <v>745990.38</v>
@@ -9180,11 +9183,11 @@
       <c r="O44" s="190">
         <v>0</v>
       </c>
-      <c r="P44" s="415">
+      <c r="P44" s="409">
         <f t="shared" si="14"/>
         <v>751681.39</v>
       </c>
-      <c r="Q44" s="415"/>
+      <c r="Q44" s="409"/>
       <c r="R44" s="232">
         <f t="shared" si="15"/>
         <v>774480.39</v>
@@ -9254,11 +9257,11 @@
       <c r="O45" s="190">
         <v>0</v>
       </c>
-      <c r="P45" s="415">
+      <c r="P45" s="409">
         <f t="shared" si="14"/>
         <v>751681.4</v>
       </c>
-      <c r="Q45" s="415"/>
+      <c r="Q45" s="409"/>
       <c r="R45" s="232">
         <f t="shared" si="15"/>
         <v>774480.4</v>
@@ -9325,11 +9328,11 @@
       <c r="O46" s="190">
         <v>0</v>
       </c>
-      <c r="P46" s="415">
+      <c r="P46" s="409">
         <f t="shared" si="14"/>
         <v>729553.41</v>
       </c>
-      <c r="Q46" s="415"/>
+      <c r="Q46" s="409"/>
       <c r="R46" s="232">
         <f t="shared" si="15"/>
         <v>751681.41</v>
@@ -9400,11 +9403,11 @@
       <c r="O47" s="190">
         <v>0</v>
       </c>
-      <c r="P47" s="415">
+      <c r="P47" s="409">
         <f t="shared" si="14"/>
         <v>751681.42</v>
       </c>
-      <c r="Q47" s="415"/>
+      <c r="Q47" s="409"/>
       <c r="R47" s="232">
         <f t="shared" si="15"/>
         <v>774480.42</v>
@@ -9475,11 +9478,11 @@
       <c r="O48" s="190">
         <v>0</v>
       </c>
-      <c r="P48" s="415">
+      <c r="P48" s="409">
         <f t="shared" si="14"/>
         <v>679072.43</v>
       </c>
-      <c r="Q48" s="415"/>
+      <c r="Q48" s="409"/>
       <c r="R48" s="232">
         <f t="shared" si="15"/>
         <v>699669.43</v>
@@ -9547,11 +9550,11 @@
       <c r="O49" s="190">
         <v>0</v>
       </c>
-      <c r="P49" s="415">
+      <c r="P49" s="409">
         <f t="shared" si="14"/>
         <v>454138.44</v>
       </c>
-      <c r="Q49" s="415"/>
+      <c r="Q49" s="409"/>
       <c r="R49" s="232">
         <f t="shared" si="15"/>
         <v>467912.44</v>
@@ -9622,11 +9625,11 @@
       <c r="O50" s="190">
         <v>0</v>
       </c>
-      <c r="P50" s="415">
+      <c r="P50" s="409">
         <f t="shared" si="14"/>
         <v>1541926.45</v>
       </c>
-      <c r="Q50" s="415"/>
+      <c r="Q50" s="409"/>
       <c r="R50" s="232">
         <f t="shared" si="15"/>
         <v>1588693.45</v>
@@ -9693,11 +9696,11 @@
       <c r="O51" s="190">
         <v>0</v>
       </c>
-      <c r="P51" s="415">
+      <c r="P51" s="409">
         <f t="shared" si="14"/>
         <v>1451354.46</v>
       </c>
-      <c r="Q51" s="415"/>
+      <c r="Q51" s="409"/>
       <c r="R51" s="232">
         <f t="shared" si="15"/>
         <v>1495374.46</v>
@@ -9765,11 +9768,11 @@
       <c r="O52" s="190">
         <v>0</v>
       </c>
-      <c r="P52" s="415">
+      <c r="P52" s="409">
         <f t="shared" si="14"/>
         <v>1526566.47</v>
       </c>
-      <c r="Q52" s="415"/>
+      <c r="Q52" s="409"/>
       <c r="R52" s="232">
         <f t="shared" si="15"/>
         <v>1572867.47</v>
@@ -9840,11 +9843,11 @@
       <c r="O53" s="190">
         <v>0</v>
       </c>
-      <c r="P53" s="415">
+      <c r="P53" s="409">
         <f t="shared" si="14"/>
         <v>1187332.48</v>
       </c>
-      <c r="Q53" s="415"/>
+      <c r="Q53" s="409"/>
       <c r="R53" s="232">
         <f t="shared" si="15"/>
         <v>1223344.48</v>
@@ -9913,11 +9916,11 @@
       <c r="O54" s="190">
         <v>0</v>
       </c>
-      <c r="P54" s="415">
+      <c r="P54" s="409">
         <f t="shared" si="14"/>
         <v>751681.49</v>
       </c>
-      <c r="Q54" s="415"/>
+      <c r="Q54" s="409"/>
       <c r="R54" s="232">
         <f t="shared" si="15"/>
         <v>774480.49</v>
@@ -9987,11 +9990,11 @@
       <c r="O55" s="190">
         <v>0</v>
       </c>
-      <c r="P55" s="415">
+      <c r="P55" s="409">
         <f t="shared" si="14"/>
         <v>729573.5</v>
       </c>
-      <c r="Q55" s="415"/>
+      <c r="Q55" s="409"/>
       <c r="R55" s="232">
         <f t="shared" si="15"/>
         <v>751701.5</v>
@@ -10059,11 +10062,11 @@
       <c r="O56" s="190">
         <v>0</v>
       </c>
-      <c r="P56" s="415">
+      <c r="P56" s="409">
         <f t="shared" si="14"/>
         <v>1526382.51</v>
       </c>
-      <c r="Q56" s="415"/>
+      <c r="Q56" s="409"/>
       <c r="R56" s="232">
         <f t="shared" si="15"/>
         <v>1572678.51</v>
@@ -10134,11 +10137,11 @@
       <c r="O57" s="190">
         <v>0</v>
       </c>
-      <c r="P57" s="415">
+      <c r="P57" s="409">
         <f t="shared" si="14"/>
         <v>759748.52</v>
       </c>
-      <c r="Q57" s="415"/>
+      <c r="Q57" s="409"/>
       <c r="R57" s="232">
         <f t="shared" si="15"/>
         <v>782792.52</v>
@@ -10206,11 +10209,11 @@
       <c r="O58" s="190">
         <v>0</v>
       </c>
-      <c r="P58" s="415">
+      <c r="P58" s="409">
         <f t="shared" si="14"/>
         <v>3029714.53</v>
       </c>
-      <c r="Q58" s="415"/>
+      <c r="Q58" s="409"/>
       <c r="R58" s="232">
         <f t="shared" si="15"/>
         <v>3121606.53</v>
@@ -10278,11 +10281,11 @@
       <c r="O59" s="190">
         <v>0</v>
       </c>
-      <c r="P59" s="415">
+      <c r="P59" s="409">
         <f t="shared" si="14"/>
         <v>751681.54</v>
       </c>
-      <c r="Q59" s="415"/>
+      <c r="Q59" s="409"/>
       <c r="R59" s="232">
         <f t="shared" si="15"/>
         <v>774480.54</v>
@@ -10352,11 +10355,11 @@
       <c r="O60" s="190">
         <v>0</v>
       </c>
-      <c r="P60" s="415">
+      <c r="P60" s="409">
         <f t="shared" si="14"/>
         <v>729553.55</v>
       </c>
-      <c r="Q60" s="415"/>
+      <c r="Q60" s="409"/>
       <c r="R60" s="232">
         <f t="shared" si="15"/>
         <v>751681.55</v>
@@ -10426,11 +10429,11 @@
       <c r="O61" s="190">
         <v>0</v>
       </c>
-      <c r="P61" s="415">
+      <c r="P61" s="409">
         <f t="shared" si="14"/>
         <v>1299606.56</v>
       </c>
-      <c r="Q61" s="415"/>
+      <c r="Q61" s="409"/>
       <c r="R61" s="232">
         <f t="shared" si="15"/>
         <v>1339024.56</v>
@@ -10500,11 +10503,11 @@
       <c r="O62" s="190">
         <v>0</v>
       </c>
-      <c r="P62" s="415">
+      <c r="P62" s="409">
         <f t="shared" si="14"/>
         <v>706083.57</v>
       </c>
-      <c r="Q62" s="415"/>
+      <c r="Q62" s="409"/>
       <c r="R62" s="232">
         <f t="shared" si="15"/>
         <v>727499.57</v>
@@ -10571,11 +10574,11 @@
       <c r="O63" s="190">
         <v>0</v>
       </c>
-      <c r="P63" s="415">
+      <c r="P63" s="409">
         <f t="shared" si="14"/>
         <v>729553.58</v>
       </c>
-      <c r="Q63" s="415"/>
+      <c r="Q63" s="409"/>
       <c r="R63" s="232">
         <f t="shared" si="15"/>
         <v>751681.58</v>
@@ -10643,11 +10646,11 @@
       <c r="O64" s="190">
         <v>0</v>
       </c>
-      <c r="P64" s="415">
+      <c r="P64" s="409">
         <f t="shared" si="14"/>
         <v>719410.59</v>
       </c>
-      <c r="Q64" s="415"/>
+      <c r="Q64" s="409"/>
       <c r="R64" s="232">
         <f t="shared" si="15"/>
         <v>741230.59</v>
@@ -10717,11 +10720,11 @@
       <c r="O65" s="190">
         <v>0</v>
       </c>
-      <c r="P65" s="415">
+      <c r="P65" s="409">
         <f t="shared" si="14"/>
         <v>749870.6</v>
       </c>
-      <c r="Q65" s="415"/>
+      <c r="Q65" s="409"/>
       <c r="R65" s="232">
         <f t="shared" si="15"/>
         <v>772614.6</v>
@@ -10791,11 +10794,11 @@
       <c r="O66" s="190">
         <v>0</v>
       </c>
-      <c r="P66" s="415">
+      <c r="P66" s="409">
         <f t="shared" si="14"/>
         <v>751362.61</v>
       </c>
-      <c r="Q66" s="415"/>
+      <c r="Q66" s="409"/>
       <c r="R66" s="232">
         <f t="shared" si="15"/>
         <v>774151.61</v>
@@ -10866,11 +10869,11 @@
       <c r="O67" s="190">
         <v>0</v>
       </c>
-      <c r="P67" s="415">
+      <c r="P67" s="409">
         <f t="shared" si="14"/>
         <v>719410.62</v>
       </c>
-      <c r="Q67" s="415"/>
+      <c r="Q67" s="409"/>
       <c r="R67" s="232">
         <f t="shared" si="15"/>
         <v>741230.62</v>
@@ -10938,11 +10941,11 @@
       <c r="O68" s="284">
         <v>97321.42</v>
       </c>
-      <c r="P68" s="415">
+      <c r="P68" s="409">
         <f t="shared" si="14"/>
         <v>849002.63</v>
       </c>
-      <c r="Q68" s="415"/>
+      <c r="Q68" s="409"/>
       <c r="R68" s="232">
         <f t="shared" si="15"/>
         <v>874753.63</v>
@@ -11012,11 +11015,11 @@
       <c r="O69" s="190">
         <v>0</v>
       </c>
-      <c r="P69" s="415">
+      <c r="P69" s="409">
         <f t="shared" si="14"/>
         <v>775184.64</v>
       </c>
-      <c r="Q69" s="415"/>
+      <c r="Q69" s="409"/>
       <c r="R69" s="232">
         <f t="shared" si="15"/>
         <v>798696.64</v>
@@ -11087,11 +11090,11 @@
       <c r="O70" s="190">
         <v>0</v>
       </c>
-      <c r="P70" s="415">
+      <c r="P70" s="409">
         <f t="shared" ref="P70:P101" si="22">ROUND(SUM(G70:O70),0) + S70</f>
         <v>751681.65</v>
       </c>
-      <c r="Q70" s="415"/>
+      <c r="Q70" s="409"/>
       <c r="R70" s="232">
         <f t="shared" ref="R70:R101" si="23">ROUND(P70+P70*3.033%,0) + S70</f>
         <v>774480.65</v>
@@ -11159,11 +11162,11 @@
       <c r="O71" s="190">
         <v>0</v>
       </c>
-      <c r="P71" s="415">
+      <c r="P71" s="409">
         <f t="shared" si="22"/>
         <v>751681.66</v>
       </c>
-      <c r="Q71" s="415"/>
+      <c r="Q71" s="409"/>
       <c r="R71" s="232">
         <f t="shared" si="23"/>
         <v>774480.66</v>
@@ -11233,11 +11236,11 @@
       <c r="O72" s="190">
         <v>0</v>
       </c>
-      <c r="P72" s="415">
+      <c r="P72" s="409">
         <f t="shared" si="22"/>
         <v>775165.67</v>
       </c>
-      <c r="Q72" s="415"/>
+      <c r="Q72" s="409"/>
       <c r="R72" s="232">
         <f t="shared" si="23"/>
         <v>798676.67</v>
@@ -11304,11 +11307,11 @@
       <c r="O73" s="190">
         <v>0</v>
       </c>
-      <c r="P73" s="415">
+      <c r="P73" s="409">
         <f t="shared" si="22"/>
         <v>2411304.6800000002</v>
       </c>
-      <c r="Q73" s="415"/>
+      <c r="Q73" s="409"/>
       <c r="R73" s="232">
         <f t="shared" si="23"/>
         <v>2484440.6800000002</v>
@@ -11375,11 +11378,11 @@
       <c r="O74" s="190">
         <v>0</v>
       </c>
-      <c r="P74" s="415">
+      <c r="P74" s="409">
         <f t="shared" si="22"/>
         <v>679072.69</v>
       </c>
-      <c r="Q74" s="415"/>
+      <c r="Q74" s="409"/>
       <c r="R74" s="232">
         <f t="shared" si="23"/>
         <v>699669.69</v>
@@ -11446,11 +11449,11 @@
       <c r="O75" s="190">
         <v>0</v>
       </c>
-      <c r="P75" s="415">
+      <c r="P75" s="409">
         <f t="shared" si="22"/>
         <v>2705004.7</v>
       </c>
-      <c r="Q75" s="415"/>
+      <c r="Q75" s="409"/>
       <c r="R75" s="232">
         <f t="shared" si="23"/>
         <v>2787047.7</v>
@@ -11519,11 +11522,11 @@
       <c r="O76" s="190">
         <v>0</v>
       </c>
-      <c r="P76" s="415">
+      <c r="P76" s="409">
         <f t="shared" si="22"/>
         <v>1445093.71</v>
       </c>
-      <c r="Q76" s="415"/>
+      <c r="Q76" s="409"/>
       <c r="R76" s="232">
         <f t="shared" si="23"/>
         <v>1488923.71</v>
@@ -11592,11 +11595,11 @@
       <c r="O77" s="190">
         <v>0</v>
       </c>
-      <c r="P77" s="415">
+      <c r="P77" s="409">
         <f t="shared" si="22"/>
         <v>709083.72</v>
       </c>
-      <c r="Q77" s="415"/>
+      <c r="Q77" s="409"/>
       <c r="R77" s="232">
         <f t="shared" si="23"/>
         <v>730590.71999999997</v>
@@ -11665,11 +11668,11 @@
       <c r="O78" s="190">
         <v>0</v>
       </c>
-      <c r="P78" s="415">
+      <c r="P78" s="409">
         <f t="shared" si="22"/>
         <v>710375.73</v>
       </c>
-      <c r="Q78" s="415"/>
+      <c r="Q78" s="409"/>
       <c r="R78" s="232">
         <f t="shared" si="23"/>
         <v>731921.73</v>
@@ -11736,11 +11739,11 @@
       <c r="O79" s="190">
         <v>0</v>
       </c>
-      <c r="P79" s="415">
+      <c r="P79" s="409">
         <f t="shared" si="22"/>
         <v>743613.74</v>
       </c>
-      <c r="Q79" s="415"/>
+      <c r="Q79" s="409"/>
       <c r="R79" s="232">
         <f t="shared" si="23"/>
         <v>766168.74</v>
@@ -11807,11 +11810,11 @@
       <c r="O80" s="190">
         <v>0</v>
       </c>
-      <c r="P80" s="415">
+      <c r="P80" s="409">
         <f t="shared" si="22"/>
         <v>719410.75</v>
       </c>
-      <c r="Q80" s="415"/>
+      <c r="Q80" s="409"/>
       <c r="R80" s="232">
         <f t="shared" si="23"/>
         <v>741230.75</v>
@@ -11882,11 +11885,11 @@
         <f>I81/2</f>
         <v>181520.91881999999</v>
       </c>
-      <c r="P81" s="415">
+      <c r="P81" s="409">
         <f t="shared" si="22"/>
         <v>933202.76</v>
       </c>
-      <c r="Q81" s="415"/>
+      <c r="Q81" s="409"/>
       <c r="R81" s="232">
         <f t="shared" si="23"/>
         <v>961507.76</v>
@@ -11952,11 +11955,11 @@
       <c r="O82" s="190">
         <v>0</v>
       </c>
-      <c r="P82" s="415">
+      <c r="P82" s="409">
         <f t="shared" si="22"/>
         <v>880384.77</v>
       </c>
-      <c r="Q82" s="415"/>
+      <c r="Q82" s="409"/>
       <c r="R82" s="232">
         <f t="shared" si="23"/>
         <v>907087.77</v>
@@ -12025,11 +12028,11 @@
       <c r="O83" s="190">
         <v>0</v>
       </c>
-      <c r="P83" s="415">
+      <c r="P83" s="409">
         <f t="shared" si="22"/>
         <v>752165.78</v>
       </c>
-      <c r="Q83" s="415"/>
+      <c r="Q83" s="409"/>
       <c r="R83" s="232">
         <f t="shared" si="23"/>
         <v>774979.78</v>
@@ -12096,11 +12099,11 @@
       <c r="O84" s="190">
         <v>0</v>
       </c>
-      <c r="P84" s="415">
+      <c r="P84" s="409">
         <f t="shared" si="22"/>
         <v>1615178.79</v>
       </c>
-      <c r="Q84" s="415"/>
+      <c r="Q84" s="409"/>
       <c r="R84" s="232">
         <f t="shared" si="23"/>
         <v>1664167.79</v>
@@ -12173,11 +12176,11 @@
       <c r="O85" s="190">
         <v>0</v>
       </c>
-      <c r="P85" s="415">
+      <c r="P85" s="409">
         <f t="shared" si="22"/>
         <v>751681.8</v>
       </c>
-      <c r="Q85" s="415"/>
+      <c r="Q85" s="409"/>
       <c r="R85" s="232">
         <f t="shared" si="23"/>
         <v>774480.8</v>
@@ -12247,11 +12250,11 @@
       <c r="O86" s="190">
         <v>0</v>
       </c>
-      <c r="P86" s="415">
+      <c r="P86" s="409">
         <f t="shared" si="22"/>
         <v>681152.81</v>
       </c>
-      <c r="Q86" s="415"/>
+      <c r="Q86" s="409"/>
       <c r="R86" s="232">
         <f t="shared" si="23"/>
         <v>701812.81</v>
@@ -12320,11 +12323,11 @@
       <c r="O87" s="190">
         <v>0</v>
       </c>
-      <c r="P87" s="415">
+      <c r="P87" s="409">
         <f t="shared" si="22"/>
         <v>635662.81999999995</v>
       </c>
-      <c r="Q87" s="415"/>
+      <c r="Q87" s="409"/>
       <c r="R87" s="232">
         <f t="shared" si="23"/>
         <v>654942.81999999995</v>
@@ -12394,11 +12397,11 @@
       <c r="O88" s="190">
         <v>0</v>
       </c>
-      <c r="P88" s="415">
+      <c r="P88" s="409">
         <f t="shared" si="22"/>
         <v>753043.83</v>
       </c>
-      <c r="Q88" s="415"/>
+      <c r="Q88" s="409"/>
       <c r="R88" s="232">
         <f t="shared" si="23"/>
         <v>775884.83</v>
@@ -12464,11 +12467,11 @@
       <c r="O89" s="190">
         <v>0</v>
       </c>
-      <c r="P89" s="415">
+      <c r="P89" s="409">
         <f t="shared" si="22"/>
         <v>753043.84</v>
       </c>
-      <c r="Q89" s="415"/>
+      <c r="Q89" s="409"/>
       <c r="R89" s="232">
         <f t="shared" si="23"/>
         <v>775884.84</v>
@@ -12535,11 +12538,11 @@
       <c r="O90" s="190">
         <v>0</v>
       </c>
-      <c r="P90" s="415">
+      <c r="P90" s="409">
         <f t="shared" si="22"/>
         <v>775884.85</v>
       </c>
-      <c r="Q90" s="415"/>
+      <c r="Q90" s="409"/>
       <c r="R90" s="232">
         <f t="shared" si="23"/>
         <v>799417.85</v>
@@ -12609,11 +12612,11 @@
       <c r="O91" s="190">
         <v>0</v>
       </c>
-      <c r="P91" s="415">
+      <c r="P91" s="409">
         <f t="shared" si="22"/>
         <v>1042170.86</v>
       </c>
-      <c r="Q91" s="415"/>
+      <c r="Q91" s="409"/>
       <c r="R91" s="232">
         <f t="shared" si="23"/>
         <v>1073780.8600000001</v>
@@ -12683,11 +12686,11 @@
       <c r="O92" s="190">
         <v>0</v>
       </c>
-      <c r="P92" s="415">
+      <c r="P92" s="409">
         <f t="shared" si="22"/>
         <v>775884.87</v>
       </c>
-      <c r="Q92" s="415"/>
+      <c r="Q92" s="409"/>
       <c r="R92" s="232">
         <f t="shared" si="23"/>
         <v>799417.87</v>
@@ -12754,11 +12757,11 @@
       <c r="O93" s="190">
         <v>0</v>
       </c>
-      <c r="P93" s="415">
+      <c r="P93" s="409">
         <f t="shared" si="22"/>
         <v>775884.88</v>
       </c>
-      <c r="Q93" s="415"/>
+      <c r="Q93" s="409"/>
       <c r="R93" s="232">
         <f t="shared" si="23"/>
         <v>799417.88</v>
@@ -12825,11 +12828,11 @@
       <c r="O94" s="190">
         <v>0</v>
       </c>
-      <c r="P94" s="415">
+      <c r="P94" s="409">
         <f t="shared" si="22"/>
         <v>775884.89</v>
       </c>
-      <c r="Q94" s="415"/>
+      <c r="Q94" s="409"/>
       <c r="R94" s="232">
         <f t="shared" si="23"/>
         <v>799417.89</v>
@@ -12899,11 +12902,11 @@
       <c r="O95" s="190">
         <v>0</v>
       </c>
-      <c r="P95" s="415">
+      <c r="P95" s="409">
         <f t="shared" si="22"/>
         <v>1239985.8999999999</v>
       </c>
-      <c r="Q95" s="415"/>
+      <c r="Q95" s="409"/>
       <c r="R95" s="232">
         <f t="shared" si="23"/>
         <v>1277595.8999999999</v>
@@ -12973,11 +12976,11 @@
       <c r="O96" s="190">
         <v>0</v>
       </c>
-      <c r="P96" s="415">
+      <c r="P96" s="409">
         <f t="shared" si="22"/>
         <v>775884.91</v>
       </c>
-      <c r="Q96" s="415"/>
+      <c r="Q96" s="409"/>
       <c r="R96" s="232">
         <f t="shared" si="23"/>
         <v>799417.91</v>
@@ -13047,11 +13050,11 @@
       <c r="O97" s="190">
         <v>0</v>
       </c>
-      <c r="P97" s="415">
+      <c r="P97" s="409">
         <f t="shared" si="22"/>
         <v>775885.92</v>
       </c>
-      <c r="Q97" s="415"/>
+      <c r="Q97" s="409"/>
       <c r="R97" s="232">
         <f t="shared" si="23"/>
         <v>799419.92</v>
@@ -13120,11 +13123,11 @@
       <c r="O98" s="190">
         <v>0</v>
       </c>
-      <c r="P98" s="415">
+      <c r="P98" s="409">
         <f t="shared" si="22"/>
         <v>741966.93</v>
       </c>
-      <c r="Q98" s="415"/>
+      <c r="Q98" s="409"/>
       <c r="R98" s="232">
         <f t="shared" si="23"/>
         <v>764471.93</v>
@@ -13194,11 +13197,11 @@
       <c r="O99" s="190">
         <v>0</v>
       </c>
-      <c r="P99" s="415">
+      <c r="P99" s="409">
         <f t="shared" si="22"/>
         <v>775884.94</v>
       </c>
-      <c r="Q99" s="415"/>
+      <c r="Q99" s="409"/>
       <c r="R99" s="232">
         <f t="shared" si="23"/>
         <v>799418.94</v>
@@ -13265,11 +13268,11 @@
       <c r="O100" s="190">
         <v>0</v>
       </c>
-      <c r="P100" s="415">
+      <c r="P100" s="409">
         <f t="shared" si="22"/>
         <v>5281372.95</v>
       </c>
-      <c r="Q100" s="415"/>
+      <c r="Q100" s="409"/>
       <c r="R100" s="232">
         <f t="shared" si="23"/>
         <v>5441557.9500000002</v>
@@ -13335,11 +13338,11 @@
       <c r="O101" s="190">
         <v>0</v>
       </c>
-      <c r="P101" s="415">
+      <c r="P101" s="409">
         <f t="shared" si="22"/>
         <v>750043.96</v>
       </c>
-      <c r="Q101" s="415"/>
+      <c r="Q101" s="409"/>
       <c r="R101" s="232">
         <f t="shared" si="23"/>
         <v>772793.96</v>
@@ -13408,11 +13411,11 @@
       <c r="O102" s="190">
         <v>0</v>
       </c>
-      <c r="P102" s="415">
+      <c r="P102" s="409">
         <f t="shared" ref="P102:P133" si="32">ROUND(SUM(G102:O102),0) + S102</f>
         <v>753062.97</v>
       </c>
-      <c r="Q102" s="415"/>
+      <c r="Q102" s="409"/>
       <c r="R102" s="232">
         <f t="shared" ref="R102:R133" si="33">ROUND(P102+P102*3.033%,0) + S102</f>
         <v>775903.97</v>
@@ -13482,11 +13485,11 @@
       <c r="O103" s="190">
         <v>0</v>
       </c>
-      <c r="P103" s="415">
+      <c r="P103" s="409">
         <f t="shared" si="32"/>
         <v>775884.98</v>
       </c>
-      <c r="Q103" s="415"/>
+      <c r="Q103" s="409"/>
       <c r="R103" s="232">
         <f t="shared" si="33"/>
         <v>799418.98</v>
@@ -13553,11 +13556,11 @@
       <c r="O104" s="190">
         <v>0</v>
       </c>
-      <c r="P104" s="415">
+      <c r="P104" s="409">
         <f t="shared" si="32"/>
         <v>775884.99</v>
       </c>
-      <c r="Q104" s="415"/>
+      <c r="Q104" s="409"/>
       <c r="R104" s="232">
         <f t="shared" si="33"/>
         <v>799418.99</v>
@@ -13627,11 +13630,11 @@
       <c r="O105" s="190">
         <v>0</v>
       </c>
-      <c r="P105" s="415">
+      <c r="P105" s="409">
         <f t="shared" si="32"/>
         <v>775885</v>
       </c>
-      <c r="Q105" s="415"/>
+      <c r="Q105" s="409"/>
       <c r="R105" s="232">
         <f t="shared" si="33"/>
         <v>799419</v>
@@ -13697,11 +13700,11 @@
       <c r="O106" s="190">
         <v>0</v>
       </c>
-      <c r="P106" s="415">
+      <c r="P106" s="409">
         <f t="shared" si="32"/>
         <v>752351.01</v>
       </c>
-      <c r="Q106" s="415"/>
+      <c r="Q106" s="409"/>
       <c r="R106" s="232">
         <f t="shared" si="33"/>
         <v>775171.01</v>
@@ -13767,11 +13770,11 @@
       <c r="O107" s="190">
         <v>0</v>
       </c>
-      <c r="P107" s="415">
+      <c r="P107" s="409">
         <f t="shared" si="32"/>
         <v>762773.02</v>
       </c>
-      <c r="Q107" s="415"/>
+      <c r="Q107" s="409"/>
       <c r="R107" s="232">
         <f t="shared" si="33"/>
         <v>785909.02</v>
@@ -13838,11 +13841,11 @@
       <c r="O108" s="190">
         <v>0</v>
       </c>
-      <c r="P108" s="415">
+      <c r="P108" s="409">
         <f t="shared" si="32"/>
         <v>1551461.03</v>
       </c>
-      <c r="Q108" s="415"/>
+      <c r="Q108" s="409"/>
       <c r="R108" s="232">
         <f t="shared" si="33"/>
         <v>1598518.03</v>
@@ -13908,11 +13911,11 @@
       <c r="O109" s="190">
         <v>0</v>
       </c>
-      <c r="P109" s="415">
+      <c r="P109" s="409">
         <f t="shared" si="32"/>
         <v>745172.04</v>
       </c>
-      <c r="Q109" s="415"/>
+      <c r="Q109" s="409"/>
       <c r="R109" s="232">
         <f t="shared" si="33"/>
         <v>767774.04</v>
@@ -13982,11 +13985,11 @@
       <c r="O110" s="190">
         <v>0</v>
       </c>
-      <c r="P110" s="415">
+      <c r="P110" s="409">
         <f t="shared" si="32"/>
         <v>727029.05</v>
       </c>
-      <c r="Q110" s="415"/>
+      <c r="Q110" s="409"/>
       <c r="R110" s="232">
         <f t="shared" si="33"/>
         <v>749081.05</v>
@@ -14057,11 +14060,11 @@
       <c r="O111" s="190">
         <v>0</v>
       </c>
-      <c r="P111" s="415">
+      <c r="P111" s="409">
         <f t="shared" si="32"/>
         <v>1169583.06</v>
       </c>
-      <c r="Q111" s="415"/>
+      <c r="Q111" s="409"/>
       <c r="R111" s="232">
         <f t="shared" si="33"/>
         <v>1205058.06</v>
@@ -14131,11 +14134,11 @@
       <c r="O112" s="190">
         <v>0</v>
       </c>
-      <c r="P112" s="415">
+      <c r="P112" s="409">
         <f t="shared" si="32"/>
         <v>743614.07</v>
       </c>
-      <c r="Q112" s="415"/>
+      <c r="Q112" s="409"/>
       <c r="R112" s="232">
         <f t="shared" si="33"/>
         <v>766169.07</v>
@@ -14205,11 +14208,11 @@
       <c r="O113" s="190">
         <v>0</v>
       </c>
-      <c r="P113" s="415">
+      <c r="P113" s="409">
         <f t="shared" si="32"/>
         <v>743614.08</v>
       </c>
-      <c r="Q113" s="415"/>
+      <c r="Q113" s="409"/>
       <c r="R113" s="232">
         <f t="shared" si="33"/>
         <v>766169.08</v>
@@ -14225,11 +14228,11 @@
     </row>
     <row r="114" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="259"/>
-      <c r="B114" s="16">
+      <c r="B114" s="166">
         <f t="shared" si="30"/>
         <v>109</v>
       </c>
-      <c r="C114" s="16" t="s">
+      <c r="C114" s="166" t="s">
         <v>118</v>
       </c>
       <c r="D114" s="74">
@@ -14275,11 +14278,11 @@
       <c r="O114" s="190">
         <v>0</v>
       </c>
-      <c r="P114" s="415">
+      <c r="P114" s="409">
         <f t="shared" si="32"/>
         <v>1550118.09</v>
       </c>
-      <c r="Q114" s="415"/>
+      <c r="Q114" s="409"/>
       <c r="R114" s="232">
         <f t="shared" si="33"/>
         <v>1597134.09</v>
@@ -14348,11 +14351,11 @@
       <c r="O115" s="190">
         <v>0</v>
       </c>
-      <c r="P115" s="415">
+      <c r="P115" s="409">
         <f t="shared" si="32"/>
         <v>737207.1</v>
       </c>
-      <c r="Q115" s="415"/>
+      <c r="Q115" s="409"/>
       <c r="R115" s="232">
         <f t="shared" si="33"/>
         <v>759568.1</v>
@@ -14423,11 +14426,11 @@
       <c r="O116" s="190">
         <v>0</v>
       </c>
-      <c r="P116" s="415">
+      <c r="P116" s="409">
         <f t="shared" si="32"/>
         <v>751682.11</v>
       </c>
-      <c r="Q116" s="415"/>
+      <c r="Q116" s="409"/>
       <c r="R116" s="232">
         <f t="shared" si="33"/>
         <v>774482.11</v>
@@ -14493,11 +14496,11 @@
       <c r="O117" s="190">
         <v>0</v>
       </c>
-      <c r="P117" s="415">
+      <c r="P117" s="409">
         <f t="shared" si="32"/>
         <v>751364.12</v>
       </c>
-      <c r="Q117" s="415"/>
+      <c r="Q117" s="409"/>
       <c r="R117" s="232">
         <f t="shared" si="33"/>
         <v>774154.12</v>
@@ -14566,11 +14569,11 @@
       <c r="O118" s="190">
         <v>0</v>
       </c>
-      <c r="P118" s="415">
+      <c r="P118" s="409">
         <f t="shared" si="32"/>
         <v>744528.13</v>
       </c>
-      <c r="Q118" s="415"/>
+      <c r="Q118" s="409"/>
       <c r="R118" s="232">
         <f t="shared" si="33"/>
         <v>767111.13</v>
@@ -14637,11 +14640,11 @@
       <c r="O119" s="190">
         <v>0</v>
       </c>
-      <c r="P119" s="415">
+      <c r="P119" s="409">
         <f t="shared" si="32"/>
         <v>751682.14</v>
       </c>
-      <c r="Q119" s="415"/>
+      <c r="Q119" s="409"/>
       <c r="R119" s="232">
         <f t="shared" si="33"/>
         <v>774482.14</v>
@@ -14708,11 +14711,11 @@
       <c r="O120" s="190">
         <v>0</v>
       </c>
-      <c r="P120" s="415">
+      <c r="P120" s="409">
         <f t="shared" si="32"/>
         <v>904966.15</v>
       </c>
-      <c r="Q120" s="415"/>
+      <c r="Q120" s="409"/>
       <c r="R120" s="232">
         <f t="shared" si="33"/>
         <v>932415.15</v>
@@ -14781,11 +14784,11 @@
       <c r="O121" s="190">
         <v>0</v>
       </c>
-      <c r="P121" s="415">
+      <c r="P121" s="409">
         <f t="shared" si="32"/>
         <v>831346.16</v>
       </c>
-      <c r="Q121" s="415"/>
+      <c r="Q121" s="409"/>
       <c r="R121" s="232">
         <f t="shared" si="33"/>
         <v>856562.16</v>
@@ -14852,11 +14855,11 @@
       <c r="O122" s="190">
         <v>0</v>
       </c>
-      <c r="P122" s="415">
+      <c r="P122" s="409">
         <f t="shared" si="32"/>
         <v>880763.17</v>
       </c>
-      <c r="Q122" s="415"/>
+      <c r="Q122" s="409"/>
       <c r="R122" s="232">
         <f t="shared" si="33"/>
         <v>907478.17</v>
@@ -14926,11 +14929,11 @@
       <c r="O123" s="190">
         <v>0</v>
       </c>
-      <c r="P123" s="415">
+      <c r="P123" s="409">
         <f t="shared" si="32"/>
         <v>855682.18</v>
       </c>
-      <c r="Q123" s="415"/>
+      <c r="Q123" s="409"/>
       <c r="R123" s="232">
         <f t="shared" si="33"/>
         <v>881636.18</v>
@@ -14999,11 +15002,11 @@
       <c r="O124" s="190">
         <v>0</v>
       </c>
-      <c r="P124" s="415">
+      <c r="P124" s="409">
         <f t="shared" si="32"/>
         <v>823834.19</v>
       </c>
-      <c r="Q124" s="415"/>
+      <c r="Q124" s="409"/>
       <c r="R124" s="232">
         <f t="shared" si="33"/>
         <v>848822.19</v>
@@ -15073,11 +15076,11 @@
       <c r="O125" s="190">
         <v>0</v>
       </c>
-      <c r="P125" s="415">
+      <c r="P125" s="409">
         <f t="shared" si="32"/>
         <v>759749.2</v>
       </c>
-      <c r="Q125" s="415"/>
+      <c r="Q125" s="409"/>
       <c r="R125" s="232">
         <f t="shared" si="33"/>
         <v>782793.2</v>
@@ -15147,11 +15150,11 @@
       <c r="O126" s="190">
         <v>0</v>
       </c>
-      <c r="P126" s="415">
+      <c r="P126" s="409">
         <f t="shared" si="32"/>
         <v>759749.21</v>
       </c>
-      <c r="Q126" s="415"/>
+      <c r="Q126" s="409"/>
       <c r="R126" s="232">
         <f t="shared" si="33"/>
         <v>782793.21</v>
@@ -15221,11 +15224,11 @@
       <c r="O127" s="190">
         <v>0</v>
       </c>
-      <c r="P127" s="415">
+      <c r="P127" s="409">
         <f t="shared" si="32"/>
         <v>759749.22</v>
       </c>
-      <c r="Q127" s="415"/>
+      <c r="Q127" s="409"/>
       <c r="R127" s="232">
         <f t="shared" si="33"/>
         <v>782793.22</v>
@@ -15292,11 +15295,11 @@
       <c r="O128" s="190">
         <v>0</v>
       </c>
-      <c r="P128" s="415">
+      <c r="P128" s="409">
         <f t="shared" si="32"/>
         <v>759749.23</v>
       </c>
-      <c r="Q128" s="415"/>
+      <c r="Q128" s="409"/>
       <c r="R128" s="232">
         <f t="shared" si="33"/>
         <v>782793.23</v>
@@ -15365,11 +15368,11 @@
       <c r="O129" s="190">
         <v>0</v>
       </c>
-      <c r="P129" s="415">
+      <c r="P129" s="409">
         <f t="shared" si="32"/>
         <v>737383.24</v>
       </c>
-      <c r="Q129" s="415"/>
+      <c r="Q129" s="409"/>
       <c r="R129" s="232">
         <f t="shared" si="33"/>
         <v>759749.24</v>
@@ -15436,11 +15439,11 @@
       <c r="O130" s="190">
         <v>0</v>
       </c>
-      <c r="P130" s="415">
+      <c r="P130" s="409">
         <f t="shared" si="32"/>
         <v>759749.25</v>
       </c>
-      <c r="Q130" s="415"/>
+      <c r="Q130" s="409"/>
       <c r="R130" s="232">
         <f t="shared" si="33"/>
         <v>782793.25</v>
@@ -15510,11 +15513,11 @@
       <c r="O131" s="190">
         <v>0</v>
       </c>
-      <c r="P131" s="415">
+      <c r="P131" s="409">
         <f t="shared" si="32"/>
         <v>759749.26</v>
       </c>
-      <c r="Q131" s="415"/>
+      <c r="Q131" s="409"/>
       <c r="R131" s="232">
         <f t="shared" si="33"/>
         <v>782793.26</v>
@@ -15581,11 +15584,11 @@
       <c r="O132" s="190">
         <v>0</v>
       </c>
-      <c r="P132" s="415">
+      <c r="P132" s="409">
         <f t="shared" si="32"/>
         <v>840425.27</v>
       </c>
-      <c r="Q132" s="415"/>
+      <c r="Q132" s="409"/>
       <c r="R132" s="232">
         <f t="shared" si="33"/>
         <v>865916.27</v>
@@ -15655,11 +15658,11 @@
       <c r="O133" s="190">
         <v>0</v>
       </c>
-      <c r="P133" s="415">
+      <c r="P133" s="409">
         <f t="shared" si="32"/>
         <v>880763.28</v>
       </c>
-      <c r="Q133" s="415"/>
+      <c r="Q133" s="409"/>
       <c r="R133" s="232">
         <f t="shared" si="33"/>
         <v>907478.28</v>
@@ -15726,11 +15729,11 @@
       <c r="O134" s="190">
         <v>0</v>
       </c>
-      <c r="P134" s="415">
+      <c r="P134" s="409">
         <f t="shared" ref="P134:P144" si="39">ROUND(SUM(G134:O134),0) + S134</f>
         <v>880763.29</v>
       </c>
-      <c r="Q134" s="415"/>
+      <c r="Q134" s="409"/>
       <c r="R134" s="232">
         <f t="shared" ref="R134:R144" si="40">ROUND(P134+P134*3.033%,0) + S134</f>
         <v>907478.29</v>
@@ -15799,11 +15802,11 @@
       <c r="O135" s="190">
         <v>0</v>
       </c>
-      <c r="P135" s="415">
+      <c r="P135" s="409">
         <f t="shared" si="39"/>
         <v>848344.3</v>
       </c>
-      <c r="Q135" s="415"/>
+      <c r="Q135" s="409"/>
       <c r="R135" s="232">
         <f t="shared" si="40"/>
         <v>874076.3</v>
@@ -15873,11 +15876,11 @@
       <c r="O136" s="190">
         <v>0</v>
       </c>
-      <c r="P136" s="415">
+      <c r="P136" s="409">
         <f t="shared" si="39"/>
         <v>880763.31</v>
       </c>
-      <c r="Q136" s="415"/>
+      <c r="Q136" s="409"/>
       <c r="R136" s="232">
         <f t="shared" si="40"/>
         <v>907478.31</v>
@@ -15947,11 +15950,11 @@
       <c r="O137" s="190">
         <v>0</v>
       </c>
-      <c r="P137" s="415">
+      <c r="P137" s="409">
         <f t="shared" si="39"/>
         <v>872696.31999999995</v>
       </c>
-      <c r="Q137" s="415"/>
+      <c r="Q137" s="409"/>
       <c r="R137" s="232">
         <f t="shared" si="40"/>
         <v>899166.32</v>
@@ -16021,11 +16024,11 @@
       <c r="O138" s="190">
         <v>0</v>
       </c>
-      <c r="P138" s="415">
+      <c r="P138" s="409">
         <f t="shared" si="39"/>
         <v>904966.33</v>
       </c>
-      <c r="Q138" s="415"/>
+      <c r="Q138" s="409"/>
       <c r="R138" s="232">
         <f t="shared" si="40"/>
         <v>932415.33</v>
@@ -16094,11 +16097,11 @@
       <c r="O139" s="190">
         <v>0</v>
       </c>
-      <c r="P139" s="415">
+      <c r="P139" s="409">
         <f t="shared" si="39"/>
         <v>791466.34</v>
       </c>
-      <c r="Q139" s="415"/>
+      <c r="Q139" s="409"/>
       <c r="R139" s="232">
         <f t="shared" si="40"/>
         <v>815473.34</v>
@@ -16167,11 +16170,11 @@
       <c r="O140" s="190">
         <v>0</v>
       </c>
-      <c r="P140" s="415">
+      <c r="P140" s="409">
         <f t="shared" si="39"/>
         <v>854048.35</v>
       </c>
-      <c r="Q140" s="415"/>
+      <c r="Q140" s="409"/>
       <c r="R140" s="232">
         <f t="shared" si="40"/>
         <v>879953.35</v>
@@ -16241,11 +16244,11 @@
       <c r="O141" s="190">
         <v>0</v>
       </c>
-      <c r="P141" s="415">
+      <c r="P141" s="409">
         <f t="shared" si="39"/>
         <v>888831.36</v>
       </c>
-      <c r="Q141" s="415"/>
+      <c r="Q141" s="409"/>
       <c r="R141" s="232">
         <f t="shared" si="40"/>
         <v>915791.35999999999</v>
@@ -16315,11 +16318,11 @@
       <c r="O142" s="190">
         <v>0</v>
       </c>
-      <c r="P142" s="415">
+      <c r="P142" s="409">
         <f t="shared" si="39"/>
         <v>824290.37</v>
       </c>
-      <c r="Q142" s="415"/>
+      <c r="Q142" s="409"/>
       <c r="R142" s="232">
         <f t="shared" si="40"/>
         <v>849292.37</v>
@@ -16385,11 +16388,11 @@
       <c r="O143" s="190">
         <v>0</v>
       </c>
-      <c r="P143" s="415">
+      <c r="P143" s="409">
         <f t="shared" si="39"/>
         <v>886156.38</v>
       </c>
-      <c r="Q143" s="415"/>
+      <c r="Q143" s="409"/>
       <c r="R143" s="232">
         <f t="shared" si="40"/>
         <v>913035.38</v>
@@ -16458,11 +16461,11 @@
       <c r="O144" s="190">
         <v>0</v>
       </c>
-      <c r="P144" s="415">
+      <c r="P144" s="409">
         <f t="shared" si="39"/>
         <v>880683.39</v>
       </c>
-      <c r="Q144" s="415"/>
+      <c r="Q144" s="409"/>
       <c r="R144" s="232">
         <f t="shared" si="40"/>
         <v>907396.39</v>
@@ -16509,8 +16512,8 @@
       <c r="O145" s="190">
         <v>0</v>
       </c>
-      <c r="P145" s="415"/>
-      <c r="Q145" s="415"/>
+      <c r="P145" s="409"/>
+      <c r="Q145" s="409"/>
       <c r="R145" s="233"/>
       <c r="S145" s="13">
         <f t="shared" si="41"/>
@@ -16551,8 +16554,8 @@
       <c r="O146" s="190">
         <v>0</v>
       </c>
-      <c r="P146" s="415"/>
-      <c r="Q146" s="415"/>
+      <c r="P146" s="409"/>
+      <c r="Q146" s="409"/>
       <c r="R146" s="233"/>
       <c r="S146" s="13">
         <f t="shared" si="41"/>
@@ -16586,8 +16589,8 @@
       <c r="O147" s="190">
         <v>0</v>
       </c>
-      <c r="P147" s="415"/>
-      <c r="Q147" s="415"/>
+      <c r="P147" s="409"/>
+      <c r="Q147" s="409"/>
       <c r="R147" s="233"/>
       <c r="S147" s="13">
         <f t="shared" si="41"/>
@@ -16621,8 +16624,8 @@
       <c r="O148" s="190">
         <v>0</v>
       </c>
-      <c r="P148" s="415"/>
-      <c r="Q148" s="415"/>
+      <c r="P148" s="409"/>
+      <c r="Q148" s="409"/>
       <c r="R148" s="233"/>
       <c r="S148" s="13">
         <f t="shared" si="41"/>
@@ -16685,11 +16688,11 @@
       <c r="O149" s="190">
         <v>0</v>
       </c>
-      <c r="P149" s="415">
+      <c r="P149" s="409">
         <f t="shared" ref="P149:P158" si="50">ROUND(SUM(G149:O149),0) + S149</f>
         <v>695209.46</v>
       </c>
-      <c r="Q149" s="415"/>
+      <c r="Q149" s="409"/>
       <c r="R149" s="232">
         <f t="shared" ref="R149:R158" si="51">ROUND(P149+P149*3.033%,0) + S149</f>
         <v>716296.46</v>
@@ -16752,11 +16755,11 @@
       <c r="O150" s="190">
         <v>0</v>
       </c>
-      <c r="P150" s="415">
+      <c r="P150" s="409">
         <f t="shared" si="50"/>
         <v>1139411.55</v>
       </c>
-      <c r="Q150" s="415"/>
+      <c r="Q150" s="409"/>
       <c r="R150" s="232">
         <f t="shared" si="51"/>
         <v>1173971.55</v>
@@ -16825,11 +16828,11 @@
       <c r="O151" s="190">
         <v>0</v>
       </c>
-      <c r="P151" s="415">
+      <c r="P151" s="409">
         <f t="shared" si="50"/>
         <v>759749.58</v>
       </c>
-      <c r="Q151" s="415"/>
+      <c r="Q151" s="409"/>
       <c r="R151" s="232">
         <f t="shared" si="51"/>
         <v>782794.58</v>
@@ -16895,11 +16898,11 @@
       <c r="O152" s="190">
         <v>0</v>
       </c>
-      <c r="P152" s="415">
+      <c r="P152" s="409">
         <f t="shared" si="50"/>
         <v>759749.59</v>
       </c>
-      <c r="Q152" s="415"/>
+      <c r="Q152" s="409"/>
       <c r="R152" s="232">
         <f t="shared" si="51"/>
         <v>782794.59</v>
@@ -16965,11 +16968,11 @@
       <c r="O153" s="190">
         <v>0</v>
       </c>
-      <c r="P153" s="415">
+      <c r="P153" s="409">
         <f t="shared" si="50"/>
         <v>759749.63</v>
       </c>
-      <c r="Q153" s="415"/>
+      <c r="Q153" s="409"/>
       <c r="R153" s="232">
         <f t="shared" si="51"/>
         <v>782794.63</v>
@@ -17035,11 +17038,11 @@
       <c r="O154" s="190">
         <v>0</v>
       </c>
-      <c r="P154" s="415">
+      <c r="P154" s="409">
         <f t="shared" si="50"/>
         <v>743614.68</v>
       </c>
-      <c r="Q154" s="415"/>
+      <c r="Q154" s="409"/>
       <c r="R154" s="232">
         <f t="shared" si="51"/>
         <v>766170.68</v>
@@ -17104,11 +17107,11 @@
       <c r="O155" s="190">
         <v>0</v>
       </c>
-      <c r="P155" s="415">
+      <c r="P155" s="409">
         <f t="shared" si="50"/>
         <v>736704.73</v>
       </c>
-      <c r="Q155" s="415"/>
+      <c r="Q155" s="409"/>
       <c r="R155" s="232">
         <f t="shared" si="51"/>
         <v>759050.73</v>
@@ -17176,11 +17179,11 @@
       <c r="O156" s="190">
         <v>0</v>
       </c>
-      <c r="P156" s="415">
+      <c r="P156" s="409">
         <f t="shared" si="50"/>
         <v>736704.75</v>
       </c>
-      <c r="Q156" s="415"/>
+      <c r="Q156" s="409"/>
       <c r="R156" s="232">
         <f t="shared" si="51"/>
         <v>759050.75</v>
@@ -17249,11 +17252,11 @@
       <c r="O157" s="190">
         <v>0</v>
       </c>
-      <c r="P157" s="415">
+      <c r="P157" s="409">
         <f t="shared" si="50"/>
         <v>759749.76</v>
       </c>
-      <c r="Q157" s="415"/>
+      <c r="Q157" s="409"/>
       <c r="R157" s="232">
         <f t="shared" si="51"/>
         <v>782794.76</v>
@@ -17319,11 +17322,11 @@
       <c r="O158" s="190">
         <v>0</v>
       </c>
-      <c r="P158" s="415">
+      <c r="P158" s="409">
         <f t="shared" si="50"/>
         <v>783953.04</v>
       </c>
-      <c r="Q158" s="415"/>
+      <c r="Q158" s="409"/>
       <c r="R158" s="232">
         <f t="shared" si="51"/>
         <v>807732.04</v>
@@ -17356,8 +17359,8 @@
       <c r="M159" s="22"/>
       <c r="N159" s="22"/>
       <c r="O159" s="68"/>
-      <c r="P159" s="440"/>
-      <c r="Q159" s="440"/>
+      <c r="P159" s="414"/>
+      <c r="Q159" s="414"/>
       <c r="R159" s="167"/>
       <c r="S159" s="13"/>
       <c r="T159" s="1"/>
@@ -17378,8 +17381,8 @@
       <c r="M160" s="178"/>
       <c r="N160" s="178"/>
       <c r="O160" s="229"/>
-      <c r="P160" s="441"/>
-      <c r="Q160" s="441"/>
+      <c r="P160" s="415"/>
+      <c r="Q160" s="415"/>
       <c r="R160" s="170"/>
       <c r="S160" s="13"/>
       <c r="T160" s="179"/>
@@ -17433,264 +17436,198 @@
         <f t="shared" si="54"/>
         <v>549617.08124800003</v>
       </c>
-      <c r="P161" s="438">
+      <c r="P161" s="412">
         <f>SUM(P6:P160)</f>
         <v>139057324.06999993</v>
       </c>
-      <c r="Q161" s="439"/>
+      <c r="Q161" s="413"/>
       <c r="R161" s="171">
         <f>SUM(R6:R160)</f>
         <v>143275052.06999999</v>
       </c>
-      <c r="S161" s="438"/>
-      <c r="T161" s="439"/>
+      <c r="S161" s="412"/>
+      <c r="T161" s="413"/>
     </row>
     <row r="162" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B162" s="436" t="s">
+      <c r="B162" s="410" t="s">
         <v>316</v>
       </c>
-      <c r="C162" s="436"/>
-      <c r="D162" s="436"/>
-      <c r="E162" s="436"/>
-      <c r="F162" s="436"/>
-      <c r="G162" s="436"/>
-      <c r="H162" s="436"/>
-      <c r="I162" s="436"/>
-      <c r="J162" s="436"/>
-      <c r="K162" s="436"/>
-      <c r="L162" s="436"/>
-      <c r="M162" s="436"/>
-      <c r="N162" s="436"/>
-      <c r="O162" s="436"/>
-      <c r="P162" s="436"/>
-      <c r="Q162" s="436"/>
-      <c r="R162" s="436"/>
-      <c r="S162" s="436"/>
-      <c r="T162" s="436"/>
+      <c r="C162" s="410"/>
+      <c r="D162" s="410"/>
+      <c r="E162" s="410"/>
+      <c r="F162" s="410"/>
+      <c r="G162" s="410"/>
+      <c r="H162" s="410"/>
+      <c r="I162" s="410"/>
+      <c r="J162" s="410"/>
+      <c r="K162" s="410"/>
+      <c r="L162" s="410"/>
+      <c r="M162" s="410"/>
+      <c r="N162" s="410"/>
+      <c r="O162" s="410"/>
+      <c r="P162" s="410"/>
+      <c r="Q162" s="410"/>
+      <c r="R162" s="410"/>
+      <c r="S162" s="410"/>
+      <c r="T162" s="410"/>
     </row>
     <row r="163" spans="1:20" ht="49.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B163" s="437"/>
-      <c r="C163" s="437"/>
-      <c r="D163" s="437"/>
-      <c r="E163" s="437"/>
-      <c r="F163" s="437"/>
-      <c r="G163" s="437"/>
-      <c r="H163" s="437"/>
-      <c r="I163" s="437"/>
-      <c r="J163" s="437"/>
-      <c r="K163" s="437"/>
-      <c r="L163" s="437"/>
-      <c r="M163" s="437"/>
-      <c r="N163" s="437"/>
-      <c r="O163" s="437"/>
-      <c r="P163" s="437"/>
-      <c r="Q163" s="437"/>
-      <c r="R163" s="437"/>
-      <c r="S163" s="437"/>
-      <c r="T163" s="437"/>
+      <c r="B163" s="411"/>
+      <c r="C163" s="411"/>
+      <c r="D163" s="411"/>
+      <c r="E163" s="411"/>
+      <c r="F163" s="411"/>
+      <c r="G163" s="411"/>
+      <c r="H163" s="411"/>
+      <c r="I163" s="411"/>
+      <c r="J163" s="411"/>
+      <c r="K163" s="411"/>
+      <c r="L163" s="411"/>
+      <c r="M163" s="411"/>
+      <c r="N163" s="411"/>
+      <c r="O163" s="411"/>
+      <c r="P163" s="411"/>
+      <c r="Q163" s="411"/>
+      <c r="R163" s="411"/>
+      <c r="S163" s="411"/>
+      <c r="T163" s="411"/>
     </row>
     <row r="164" spans="1:20" ht="13.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B164" s="437" t="s">
+      <c r="B164" s="411" t="s">
         <v>259</v>
       </c>
-      <c r="C164" s="437"/>
-      <c r="D164" s="437"/>
-      <c r="E164" s="437"/>
-      <c r="F164" s="437"/>
-      <c r="G164" s="437"/>
-      <c r="H164" s="437"/>
-      <c r="I164" s="437"/>
-      <c r="J164" s="437"/>
-      <c r="K164" s="437"/>
-      <c r="L164" s="437"/>
-      <c r="M164" s="437"/>
-      <c r="N164" s="437"/>
-      <c r="O164" s="437"/>
-      <c r="P164" s="437"/>
-      <c r="Q164" s="437"/>
-      <c r="R164" s="437"/>
-      <c r="S164" s="437"/>
-      <c r="T164" s="437"/>
+      <c r="C164" s="411"/>
+      <c r="D164" s="411"/>
+      <c r="E164" s="411"/>
+      <c r="F164" s="411"/>
+      <c r="G164" s="411"/>
+      <c r="H164" s="411"/>
+      <c r="I164" s="411"/>
+      <c r="J164" s="411"/>
+      <c r="K164" s="411"/>
+      <c r="L164" s="411"/>
+      <c r="M164" s="411"/>
+      <c r="N164" s="411"/>
+      <c r="O164" s="411"/>
+      <c r="P164" s="411"/>
+      <c r="Q164" s="411"/>
+      <c r="R164" s="411"/>
+      <c r="S164" s="411"/>
+      <c r="T164" s="411"/>
     </row>
     <row r="165" spans="1:20" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B165" s="437"/>
-      <c r="C165" s="437"/>
-      <c r="D165" s="437"/>
-      <c r="E165" s="437"/>
-      <c r="F165" s="437"/>
-      <c r="G165" s="437"/>
-      <c r="H165" s="437"/>
-      <c r="I165" s="437"/>
-      <c r="J165" s="437"/>
-      <c r="K165" s="437"/>
-      <c r="L165" s="437"/>
-      <c r="M165" s="437"/>
-      <c r="N165" s="437"/>
-      <c r="O165" s="437"/>
-      <c r="P165" s="437"/>
-      <c r="Q165" s="437"/>
-      <c r="R165" s="437"/>
-      <c r="S165" s="437"/>
-      <c r="T165" s="437"/>
+      <c r="B165" s="411"/>
+      <c r="C165" s="411"/>
+      <c r="D165" s="411"/>
+      <c r="E165" s="411"/>
+      <c r="F165" s="411"/>
+      <c r="G165" s="411"/>
+      <c r="H165" s="411"/>
+      <c r="I165" s="411"/>
+      <c r="J165" s="411"/>
+      <c r="K165" s="411"/>
+      <c r="L165" s="411"/>
+      <c r="M165" s="411"/>
+      <c r="N165" s="411"/>
+      <c r="O165" s="411"/>
+      <c r="P165" s="411"/>
+      <c r="Q165" s="411"/>
+      <c r="R165" s="411"/>
+      <c r="S165" s="411"/>
+      <c r="T165" s="411"/>
     </row>
     <row r="166" spans="1:20" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B166" s="437"/>
-      <c r="C166" s="437"/>
-      <c r="D166" s="437"/>
-      <c r="E166" s="437"/>
-      <c r="F166" s="437"/>
-      <c r="G166" s="437"/>
-      <c r="H166" s="437"/>
-      <c r="I166" s="437"/>
-      <c r="J166" s="437"/>
-      <c r="K166" s="437"/>
-      <c r="L166" s="437"/>
-      <c r="M166" s="437"/>
-      <c r="N166" s="437"/>
-      <c r="O166" s="437"/>
-      <c r="P166" s="437"/>
-      <c r="Q166" s="437"/>
-      <c r="R166" s="437"/>
-      <c r="S166" s="437"/>
-      <c r="T166" s="437"/>
+      <c r="B166" s="411"/>
+      <c r="C166" s="411"/>
+      <c r="D166" s="411"/>
+      <c r="E166" s="411"/>
+      <c r="F166" s="411"/>
+      <c r="G166" s="411"/>
+      <c r="H166" s="411"/>
+      <c r="I166" s="411"/>
+      <c r="J166" s="411"/>
+      <c r="K166" s="411"/>
+      <c r="L166" s="411"/>
+      <c r="M166" s="411"/>
+      <c r="N166" s="411"/>
+      <c r="O166" s="411"/>
+      <c r="P166" s="411"/>
+      <c r="Q166" s="411"/>
+      <c r="R166" s="411"/>
+      <c r="S166" s="411"/>
+      <c r="T166" s="411"/>
     </row>
     <row r="167" spans="1:20" ht="128.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B167" s="437"/>
-      <c r="C167" s="437"/>
-      <c r="D167" s="437"/>
-      <c r="E167" s="437"/>
-      <c r="F167" s="437"/>
-      <c r="G167" s="437"/>
-      <c r="H167" s="437"/>
-      <c r="I167" s="437"/>
-      <c r="J167" s="437"/>
-      <c r="K167" s="437"/>
-      <c r="L167" s="437"/>
-      <c r="M167" s="437"/>
-      <c r="N167" s="437"/>
-      <c r="O167" s="437"/>
-      <c r="P167" s="437"/>
-      <c r="Q167" s="437"/>
-      <c r="R167" s="437"/>
-      <c r="S167" s="437"/>
-      <c r="T167" s="437"/>
+      <c r="B167" s="411"/>
+      <c r="C167" s="411"/>
+      <c r="D167" s="411"/>
+      <c r="E167" s="411"/>
+      <c r="F167" s="411"/>
+      <c r="G167" s="411"/>
+      <c r="H167" s="411"/>
+      <c r="I167" s="411"/>
+      <c r="J167" s="411"/>
+      <c r="K167" s="411"/>
+      <c r="L167" s="411"/>
+      <c r="M167" s="411"/>
+      <c r="N167" s="411"/>
+      <c r="O167" s="411"/>
+      <c r="P167" s="411"/>
+      <c r="Q167" s="411"/>
+      <c r="R167" s="411"/>
+      <c r="S167" s="411"/>
+      <c r="T167" s="411"/>
     </row>
   </sheetData>
   <mergeCells count="186">
-    <mergeCell ref="P146:Q146"/>
-    <mergeCell ref="P147:Q147"/>
-    <mergeCell ref="P148:Q148"/>
-    <mergeCell ref="P149:Q149"/>
-    <mergeCell ref="P151:Q151"/>
-    <mergeCell ref="P141:Q141"/>
-    <mergeCell ref="P142:Q142"/>
-    <mergeCell ref="P143:Q143"/>
-    <mergeCell ref="P144:Q144"/>
-    <mergeCell ref="P145:Q145"/>
-    <mergeCell ref="P150:Q150"/>
-    <mergeCell ref="B162:T163"/>
-    <mergeCell ref="B164:T167"/>
-    <mergeCell ref="P157:Q157"/>
-    <mergeCell ref="P158:Q158"/>
-    <mergeCell ref="P161:Q161"/>
-    <mergeCell ref="P159:Q159"/>
-    <mergeCell ref="P160:Q160"/>
-    <mergeCell ref="P152:Q152"/>
-    <mergeCell ref="P153:Q153"/>
-    <mergeCell ref="P154:Q154"/>
-    <mergeCell ref="P155:Q155"/>
-    <mergeCell ref="P156:Q156"/>
-    <mergeCell ref="S161:T161"/>
-    <mergeCell ref="P136:Q136"/>
-    <mergeCell ref="P137:Q137"/>
-    <mergeCell ref="P138:Q138"/>
-    <mergeCell ref="P139:Q139"/>
-    <mergeCell ref="P140:Q140"/>
-    <mergeCell ref="P131:Q131"/>
-    <mergeCell ref="P132:Q132"/>
-    <mergeCell ref="P133:Q133"/>
-    <mergeCell ref="P134:Q134"/>
-    <mergeCell ref="P135:Q135"/>
-    <mergeCell ref="P126:Q126"/>
-    <mergeCell ref="P127:Q127"/>
-    <mergeCell ref="P128:Q128"/>
-    <mergeCell ref="P129:Q129"/>
-    <mergeCell ref="P130:Q130"/>
-    <mergeCell ref="P121:Q121"/>
-    <mergeCell ref="P122:Q122"/>
-    <mergeCell ref="P123:Q123"/>
-    <mergeCell ref="P124:Q124"/>
-    <mergeCell ref="P125:Q125"/>
-    <mergeCell ref="P116:Q116"/>
-    <mergeCell ref="P117:Q117"/>
-    <mergeCell ref="P118:Q118"/>
-    <mergeCell ref="P119:Q119"/>
-    <mergeCell ref="P120:Q120"/>
-    <mergeCell ref="P111:Q111"/>
-    <mergeCell ref="P112:Q112"/>
-    <mergeCell ref="P113:Q113"/>
-    <mergeCell ref="P114:Q114"/>
-    <mergeCell ref="P115:Q115"/>
-    <mergeCell ref="P106:Q106"/>
-    <mergeCell ref="P107:Q107"/>
-    <mergeCell ref="P108:Q108"/>
-    <mergeCell ref="P109:Q109"/>
-    <mergeCell ref="P110:Q110"/>
-    <mergeCell ref="P101:Q101"/>
-    <mergeCell ref="P102:Q102"/>
-    <mergeCell ref="P103:Q103"/>
-    <mergeCell ref="P104:Q104"/>
-    <mergeCell ref="P105:Q105"/>
-    <mergeCell ref="P96:Q96"/>
-    <mergeCell ref="P97:Q97"/>
-    <mergeCell ref="P98:Q98"/>
-    <mergeCell ref="P99:Q99"/>
-    <mergeCell ref="P100:Q100"/>
-    <mergeCell ref="P91:Q91"/>
-    <mergeCell ref="P92:Q92"/>
-    <mergeCell ref="P93:Q93"/>
-    <mergeCell ref="P94:Q94"/>
-    <mergeCell ref="P95:Q95"/>
-    <mergeCell ref="P86:Q86"/>
-    <mergeCell ref="P87:Q87"/>
-    <mergeCell ref="P88:Q88"/>
-    <mergeCell ref="P89:Q89"/>
-    <mergeCell ref="P90:Q90"/>
-    <mergeCell ref="P81:Q81"/>
-    <mergeCell ref="P82:Q82"/>
-    <mergeCell ref="P83:Q83"/>
-    <mergeCell ref="P84:Q84"/>
-    <mergeCell ref="P85:Q85"/>
-    <mergeCell ref="P76:Q76"/>
-    <mergeCell ref="P77:Q77"/>
-    <mergeCell ref="P78:Q78"/>
-    <mergeCell ref="P79:Q79"/>
-    <mergeCell ref="P80:Q80"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="P75:Q75"/>
-    <mergeCell ref="P66:Q66"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="P62:Q62"/>
-    <mergeCell ref="P63:Q63"/>
-    <mergeCell ref="P64:Q64"/>
-    <mergeCell ref="P65:Q65"/>
-    <mergeCell ref="P56:Q56"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="P60:Q60"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="R4:S5"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="P27:Q27"/>
     <mergeCell ref="P28:Q28"/>
     <mergeCell ref="P29:Q29"/>
@@ -17715,54 +17652,120 @@
     <mergeCell ref="P33:Q33"/>
     <mergeCell ref="P34:Q34"/>
     <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C1:L1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="A3:T3"/>
-    <mergeCell ref="R4:S5"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="P26:Q26"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="P56:Q56"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="P60:Q60"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="P66:Q66"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="P68:Q68"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="P62:Q62"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="P64:Q64"/>
+    <mergeCell ref="P65:Q65"/>
+    <mergeCell ref="P76:Q76"/>
+    <mergeCell ref="P77:Q77"/>
+    <mergeCell ref="P78:Q78"/>
+    <mergeCell ref="P79:Q79"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="P75:Q75"/>
+    <mergeCell ref="P86:Q86"/>
+    <mergeCell ref="P87:Q87"/>
+    <mergeCell ref="P88:Q88"/>
+    <mergeCell ref="P89:Q89"/>
+    <mergeCell ref="P90:Q90"/>
+    <mergeCell ref="P81:Q81"/>
+    <mergeCell ref="P82:Q82"/>
+    <mergeCell ref="P83:Q83"/>
+    <mergeCell ref="P84:Q84"/>
+    <mergeCell ref="P85:Q85"/>
+    <mergeCell ref="P96:Q96"/>
+    <mergeCell ref="P97:Q97"/>
+    <mergeCell ref="P98:Q98"/>
+    <mergeCell ref="P99:Q99"/>
+    <mergeCell ref="P100:Q100"/>
+    <mergeCell ref="P91:Q91"/>
+    <mergeCell ref="P92:Q92"/>
+    <mergeCell ref="P93:Q93"/>
+    <mergeCell ref="P94:Q94"/>
+    <mergeCell ref="P95:Q95"/>
+    <mergeCell ref="P106:Q106"/>
+    <mergeCell ref="P107:Q107"/>
+    <mergeCell ref="P108:Q108"/>
+    <mergeCell ref="P109:Q109"/>
+    <mergeCell ref="P110:Q110"/>
+    <mergeCell ref="P101:Q101"/>
+    <mergeCell ref="P102:Q102"/>
+    <mergeCell ref="P103:Q103"/>
+    <mergeCell ref="P104:Q104"/>
+    <mergeCell ref="P105:Q105"/>
+    <mergeCell ref="P116:Q116"/>
+    <mergeCell ref="P117:Q117"/>
+    <mergeCell ref="P118:Q118"/>
+    <mergeCell ref="P119:Q119"/>
+    <mergeCell ref="P120:Q120"/>
+    <mergeCell ref="P111:Q111"/>
+    <mergeCell ref="P112:Q112"/>
+    <mergeCell ref="P113:Q113"/>
+    <mergeCell ref="P114:Q114"/>
+    <mergeCell ref="P115:Q115"/>
+    <mergeCell ref="P126:Q126"/>
+    <mergeCell ref="P127:Q127"/>
+    <mergeCell ref="P128:Q128"/>
+    <mergeCell ref="P129:Q129"/>
+    <mergeCell ref="P130:Q130"/>
+    <mergeCell ref="P121:Q121"/>
+    <mergeCell ref="P122:Q122"/>
+    <mergeCell ref="P123:Q123"/>
+    <mergeCell ref="P124:Q124"/>
+    <mergeCell ref="P125:Q125"/>
+    <mergeCell ref="P136:Q136"/>
+    <mergeCell ref="P137:Q137"/>
+    <mergeCell ref="P138:Q138"/>
+    <mergeCell ref="P139:Q139"/>
+    <mergeCell ref="P140:Q140"/>
+    <mergeCell ref="P131:Q131"/>
+    <mergeCell ref="P132:Q132"/>
+    <mergeCell ref="P133:Q133"/>
+    <mergeCell ref="P134:Q134"/>
+    <mergeCell ref="P135:Q135"/>
+    <mergeCell ref="B162:T163"/>
+    <mergeCell ref="B164:T167"/>
+    <mergeCell ref="P157:Q157"/>
+    <mergeCell ref="P158:Q158"/>
+    <mergeCell ref="P161:Q161"/>
+    <mergeCell ref="P159:Q159"/>
+    <mergeCell ref="P160:Q160"/>
+    <mergeCell ref="P152:Q152"/>
+    <mergeCell ref="P153:Q153"/>
+    <mergeCell ref="P154:Q154"/>
+    <mergeCell ref="P155:Q155"/>
+    <mergeCell ref="P156:Q156"/>
+    <mergeCell ref="S161:T161"/>
+    <mergeCell ref="P146:Q146"/>
+    <mergeCell ref="P147:Q147"/>
+    <mergeCell ref="P148:Q148"/>
+    <mergeCell ref="P149:Q149"/>
+    <mergeCell ref="P151:Q151"/>
+    <mergeCell ref="P141:Q141"/>
+    <mergeCell ref="P142:Q142"/>
+    <mergeCell ref="P143:Q143"/>
+    <mergeCell ref="P144:Q144"/>
+    <mergeCell ref="P145:Q145"/>
+    <mergeCell ref="P150:Q150"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="U66" r:id="rId1" xr:uid="{60CCA824-04D7-4098-BB5B-CC4EC0E5DE92}"/>
@@ -17777,7 +17780,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D69DBA-AA88-413A-80A7-A9BAAE7F2C32}">
-  <dimension ref="B1:L228"/>
+  <dimension ref="B1:L237"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="8" max="8" width="10.88671875" customWidth="1"/>
@@ -17856,7 +17859,7 @@
     </row>
     <row r="6" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C6" s="444" t="s">
-        <v>370</v>
+        <v>477</v>
       </c>
       <c r="D6" s="445"/>
       <c r="E6" s="445"/>
@@ -17935,7 +17938,7 @@
         <v>164</v>
       </c>
       <c r="H13" s="442" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I13" s="442"/>
       <c r="J13" s="443"/>
@@ -17954,7 +17957,7 @@
     </row>
     <row r="15" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C15" s="444" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D15" s="445"/>
       <c r="E15" s="445"/>
@@ -18048,7 +18051,7 @@
     </row>
     <row r="23" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C23" s="444" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D23" s="445"/>
       <c r="E23" s="445"/>
@@ -18123,7 +18126,7 @@
         <v>164</v>
       </c>
       <c r="H30" s="442" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I30" s="442"/>
       <c r="J30" s="443"/>
@@ -18142,7 +18145,7 @@
     </row>
     <row r="32" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C32" s="444" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D32" s="445"/>
       <c r="E32" s="445"/>
@@ -18236,7 +18239,7 @@
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C41" s="444" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D41" s="445"/>
       <c r="E41" s="445"/>
@@ -18281,7 +18284,7 @@
       </c>
       <c r="H46" s="242"/>
       <c r="I46" s="243" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J46" s="244"/>
     </row>
@@ -18334,7 +18337,7 @@
     </row>
     <row r="50" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C50" s="444" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D50" s="445"/>
       <c r="E50" s="445"/>
@@ -18377,7 +18380,7 @@
       </c>
       <c r="H55" s="242"/>
       <c r="I55" s="245" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J55" s="244"/>
     </row>
@@ -18411,7 +18414,7 @@
         <v>164</v>
       </c>
       <c r="H57" s="442" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I57" s="442"/>
       <c r="J57" s="443"/>
@@ -18430,7 +18433,7 @@
     </row>
     <row r="59" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C59" s="444" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D59" s="445"/>
       <c r="E59" s="445"/>
@@ -18527,7 +18530,7 @@
     </row>
     <row r="68" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C68" s="444" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D68" s="445"/>
       <c r="E68" s="445"/>
@@ -18621,7 +18624,7 @@
     </row>
     <row r="77" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C77" s="444" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D77" s="445"/>
       <c r="E77" s="445"/>
@@ -18715,7 +18718,7 @@
     </row>
     <row r="86" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C86" s="444" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D86" s="445"/>
       <c r="E86" s="445"/>
@@ -18809,7 +18812,7 @@
     </row>
     <row r="95" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C95" s="444" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D95" s="445"/>
       <c r="E95" s="445"/>
@@ -18906,7 +18909,7 @@
     </row>
     <row r="104" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C104" s="444" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D104" s="445"/>
       <c r="E104" s="445"/>
@@ -19000,7 +19003,7 @@
     </row>
     <row r="113" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C113" s="444" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D113" s="445"/>
       <c r="E113" s="445"/>
@@ -19113,7 +19116,7 @@
     </row>
     <row r="122" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C122" s="444" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D122" s="445"/>
       <c r="E122" s="445"/>
@@ -19226,7 +19229,7 @@
     </row>
     <row r="131" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C131" s="444" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D131" s="445"/>
       <c r="E131" s="445"/>
@@ -19370,7 +19373,7 @@
     </row>
     <row r="145" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C145" s="444" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D145" s="445"/>
       <c r="E145" s="445"/>
@@ -19412,7 +19415,7 @@
         <v>163</v>
       </c>
       <c r="H150" s="242" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I150" s="243"/>
       <c r="J150" s="244"/>
@@ -19466,7 +19469,7 @@
     </row>
     <row r="154" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C154" s="444" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D154" s="445"/>
       <c r="E154" s="445"/>
@@ -19560,7 +19563,7 @@
     </row>
     <row r="163" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C163" s="444" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D163" s="445"/>
       <c r="E163" s="445"/>
@@ -19654,7 +19657,7 @@
     </row>
     <row r="172" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C172" s="444" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D172" s="445"/>
       <c r="E172" s="445"/>
@@ -19748,7 +19751,7 @@
     </row>
     <row r="181" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C181" s="444" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D181" s="445"/>
       <c r="E181" s="445"/>
@@ -19842,7 +19845,7 @@
     </row>
     <row r="190" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C190" s="444" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D190" s="445"/>
       <c r="E190" s="445"/>
@@ -19936,7 +19939,7 @@
     </row>
     <row r="199" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C199" s="444" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D199" s="445"/>
       <c r="E199" s="445"/>
@@ -20030,7 +20033,7 @@
     </row>
     <row r="208" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C208" s="444" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D208" s="445"/>
       <c r="E208" s="445"/>
@@ -20125,7 +20128,7 @@
     </row>
     <row r="217" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C217" s="444" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D217" s="445"/>
       <c r="E217" s="445"/>
@@ -20219,7 +20222,7 @@
     </row>
     <row r="226" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C226" s="444" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D226" s="445"/>
       <c r="E226" s="445"/>
@@ -20249,8 +20252,138 @@
       <c r="I228" s="451"/>
       <c r="J228" s="452"/>
     </row>
+    <row r="230" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="231" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C231" s="354" t="s">
+        <v>158</v>
+      </c>
+      <c r="D231" s="355"/>
+      <c r="E231" s="241"/>
+      <c r="F231" s="60"/>
+      <c r="G231" s="60" t="s">
+        <v>163</v>
+      </c>
+      <c r="H231" s="242"/>
+      <c r="I231" s="243"/>
+      <c r="J231" s="244"/>
+    </row>
+    <row r="232" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C232" s="356"/>
+      <c r="D232" s="357"/>
+      <c r="E232" s="246"/>
+      <c r="F232" s="35"/>
+      <c r="G232" s="35" t="s">
+        <v>331</v>
+      </c>
+      <c r="H232" s="247"/>
+      <c r="I232" s="245">
+        <f>I223+1</f>
+        <v>25</v>
+      </c>
+      <c r="J232" s="62"/>
+    </row>
+    <row r="233" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C233" s="356" t="s">
+        <v>159</v>
+      </c>
+      <c r="D233" s="357" t="s">
+        <v>160</v>
+      </c>
+      <c r="E233" s="35" t="s">
+        <v>161</v>
+      </c>
+      <c r="F233" s="35"/>
+      <c r="G233" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="H233" s="442">
+        <v>109</v>
+      </c>
+      <c r="I233" s="442"/>
+      <c r="J233" s="443"/>
+    </row>
+    <row r="234" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C234" s="356" t="s">
+        <v>162</v>
+      </c>
+      <c r="D234" s="357"/>
+      <c r="E234" s="35"/>
+      <c r="F234" s="35"/>
+      <c r="G234" s="35"/>
+      <c r="H234" s="35"/>
+      <c r="I234" s="35"/>
+      <c r="J234" s="63"/>
+    </row>
+    <row r="235" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C235" s="444" t="s">
+        <v>478</v>
+      </c>
+      <c r="D235" s="445"/>
+      <c r="E235" s="445"/>
+      <c r="F235" s="445"/>
+      <c r="G235" s="445"/>
+      <c r="H235" s="445"/>
+      <c r="I235" s="445"/>
+      <c r="J235" s="446"/>
+    </row>
+    <row r="236" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C236" s="447"/>
+      <c r="D236" s="448"/>
+      <c r="E236" s="448"/>
+      <c r="F236" s="448"/>
+      <c r="G236" s="448"/>
+      <c r="H236" s="448"/>
+      <c r="I236" s="448"/>
+      <c r="J236" s="449"/>
+    </row>
+    <row r="237" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C237" s="450"/>
+      <c r="D237" s="451"/>
+      <c r="E237" s="451"/>
+      <c r="F237" s="451"/>
+      <c r="G237" s="451"/>
+      <c r="H237" s="451"/>
+      <c r="I237" s="451"/>
+      <c r="J237" s="452"/>
+    </row>
   </sheetData>
-  <mergeCells count="50">
+  <mergeCells count="52">
+    <mergeCell ref="H233:J233"/>
+    <mergeCell ref="C235:J237"/>
+    <mergeCell ref="H206:J206"/>
+    <mergeCell ref="C208:J210"/>
+    <mergeCell ref="H215:J215"/>
+    <mergeCell ref="C217:J219"/>
+    <mergeCell ref="H161:J161"/>
+    <mergeCell ref="C163:J165"/>
+    <mergeCell ref="H170:J170"/>
+    <mergeCell ref="C172:J174"/>
+    <mergeCell ref="H188:J188"/>
+    <mergeCell ref="C190:J192"/>
+    <mergeCell ref="H197:J197"/>
+    <mergeCell ref="C199:J201"/>
+    <mergeCell ref="H179:J179"/>
+    <mergeCell ref="C181:J183"/>
+    <mergeCell ref="H66:J66"/>
+    <mergeCell ref="C68:J70"/>
+    <mergeCell ref="H102:J102"/>
+    <mergeCell ref="C104:J106"/>
+    <mergeCell ref="C95:J97"/>
+    <mergeCell ref="H84:J84"/>
+    <mergeCell ref="C86:J88"/>
+    <mergeCell ref="H93:J93"/>
+    <mergeCell ref="C32:J34"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="C41:J43"/>
+    <mergeCell ref="H48:J48"/>
+    <mergeCell ref="C50:J52"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="C6:J8"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="C23:J25"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="C15:J17"/>
     <mergeCell ref="H224:J224"/>
     <mergeCell ref="C226:J228"/>
     <mergeCell ref="H57:J57"/>
@@ -20267,40 +20400,6 @@
     <mergeCell ref="C113:J115"/>
     <mergeCell ref="H75:J75"/>
     <mergeCell ref="C77:J79"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="C6:J8"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="C23:J25"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="C15:J17"/>
-    <mergeCell ref="C32:J34"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="C41:J43"/>
-    <mergeCell ref="H48:J48"/>
-    <mergeCell ref="C50:J52"/>
-    <mergeCell ref="H66:J66"/>
-    <mergeCell ref="C68:J70"/>
-    <mergeCell ref="H102:J102"/>
-    <mergeCell ref="C104:J106"/>
-    <mergeCell ref="C95:J97"/>
-    <mergeCell ref="H84:J84"/>
-    <mergeCell ref="C86:J88"/>
-    <mergeCell ref="H93:J93"/>
-    <mergeCell ref="H206:J206"/>
-    <mergeCell ref="C208:J210"/>
-    <mergeCell ref="H215:J215"/>
-    <mergeCell ref="C217:J219"/>
-    <mergeCell ref="H161:J161"/>
-    <mergeCell ref="C163:J165"/>
-    <mergeCell ref="H170:J170"/>
-    <mergeCell ref="C172:J174"/>
-    <mergeCell ref="H188:J188"/>
-    <mergeCell ref="C190:J192"/>
-    <mergeCell ref="H197:J197"/>
-    <mergeCell ref="C199:J201"/>
-    <mergeCell ref="H179:J179"/>
-    <mergeCell ref="C181:J183"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
